--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -7723,34 +7723,34 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>8667000</v>
+        <v>7366900</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>19433</v>
+        <v>16518</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>7366950</v>
+        <v>7366900</v>
       </c>
       <c r="L103" s="5" t="n">
         <v>16518</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -9595,34 +9595,34 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
-        <v>10345000</v>
+        <v>8793200</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>21917</v>
+        <v>18630</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="5" t="n">
-        <v>8793250</v>
+        <v>8793200</v>
       </c>
       <c r="L131" s="5" t="n">
         <v>18630</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr">
@@ -13245,34 +13245,34 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>10119000</v>
+        <v>8803500</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>21439</v>
+        <v>18651</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>8601150</v>
+        <v>8803500</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>18223</v>
+        <v>18651</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -16505,23 +16505,23 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
-        <v>9900000</v>
+        <v>8415000</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>20975</v>
+        <v>17828</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K236" s="5" t="n">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -32364,7 +32364,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -51513,34 +51513,34 @@
       </c>
       <c r="F752" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G752" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H752" s="5" t="n">
-        <v>8558000</v>
+        <v>7445400</v>
       </c>
       <c r="I752" s="5" t="n">
-        <v>19231</v>
+        <v>16731</v>
       </c>
       <c r="J752" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K752" s="5" t="n">
-        <v>7274300</v>
+        <v>7445400</v>
       </c>
       <c r="L752" s="5" t="n">
-        <v>16347</v>
+        <v>16731</v>
       </c>
       <c r="M752" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N752" s="3" t="inlineStr">
@@ -57680,7 +57680,7 @@
       </c>
       <c r="G847" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H847" s="5" t="n">
@@ -58658,7 +58658,7 @@
       </c>
       <c r="G862" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H862" s="5" t="n">
@@ -70324,7 +70324,7 @@
       </c>
       <c r="G1033" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H1033" s="5" t="n">
@@ -80347,34 +80347,34 @@
       </c>
       <c r="F1183" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H1183" s="5" t="n">
-        <v>6962000</v>
+        <v>6056900</v>
       </c>
       <c r="I1183" s="5" t="n">
-        <v>20063</v>
+        <v>17455</v>
       </c>
       <c r="J1183" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1183" s="5" t="n">
-        <v>5917700</v>
+        <v>6056900</v>
       </c>
       <c r="L1183" s="5" t="n">
-        <v>17054</v>
+        <v>17455</v>
       </c>
       <c r="M1183" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1183" s="3" t="inlineStr">
@@ -80826,7 +80826,7 @@
       </c>
       <c r="G1190" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H1190" s="5" t="n">
@@ -87458,7 +87458,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87468,7 +87468,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88477,12 +88477,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$867万
-$19,433/呎
-(在售)</t>
+$737万
+$16,518/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -88529,7 +88529,7 @@
           <t>D | 446呎 (2房)
 $728万
 $16,329/呎
-(26年-08月-24日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -88688,12 +88688,12 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1034万
-$21,917/呎
-(在售)</t>
+$879万
+$18,630/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -89205,12 +89205,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1012万
-$21,439/呎
-(在售)</t>
+$880万
+$18,651/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -89492,7 +89492,7 @@
           <t>A | 472呎 (2房)
 $868万
 $18,393/呎
-(26年-08月-28日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -89675,12 +89675,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="24" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$990万
-$20,975/呎
-(在售)</t>
+$842万
+$17,828/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
@@ -89727,7 +89727,7 @@
           <t>A | 472呎 (2房)
 $840万
 $17,792/呎
-(26年-08月-28日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
@@ -90033,7 +90033,7 @@
           <t>D | 446呎 (2房)
 $694万
 $15,565/呎
-(26年-08月-24日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F58" s="24" t="inlineStr">
@@ -92007,7 +92007,7 @@
           <t>D | 554呎 (2房)
 $896万
 $16,171/呎
-(26年-08月-22日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -93420,7 +93420,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93430,7 +93430,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94768,12 +94768,12 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$856万
-$19,231/呎
-(在售)</t>
+$745万
+$16,731/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="F32" s="24" t="inlineStr">
@@ -95666,7 +95666,7 @@
           <t>D | 445呎 (2房)
 $715万
 $16,074/呎
-(26年-08月-21日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F51" s="24" t="inlineStr">
@@ -95807,7 +95807,7 @@
           <t>D | 445呎 (2房)
 $712万
 $16,004/呎
-(26年-08月-21日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="F54" s="24" t="inlineStr">
@@ -96176,7 +96176,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96186,7 +96186,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -97451,7 +97451,7 @@
           <t>B | 783呎 (3房)
 $1537万
 $19,631/呎
-(26年-08月-24日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -98864,12 +98864,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G46" s="23" t="inlineStr">
+      <c r="G46" s="24" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$696万
-$20,063/呎
-(在售)</t>
+$606万
+$17,455/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -98932,7 +98932,7 @@
           <t>F | 347呎 (1房)
 $591万
 $17,029/呎
-(26年-08月-29日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,19 +129,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -221,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -289,13 +283,10 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6387,7 +6378,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6396,10 +6387,10 @@
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>8720000</v>
+        <v>8807000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>19552</v>
+        <v>19747</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6407,10 +6398,10 @@
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>7412000</v>
+        <v>7485950</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>16619</v>
+        <v>16785</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -7055,7 +7046,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -7064,10 +7055,10 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>8693000</v>
+        <v>8780000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>19491</v>
+        <v>19686</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -7075,10 +7066,10 @@
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>7389050</v>
+        <v>7463000</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>16567</v>
+        <v>16733</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -7257,7 +7248,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -7591,7 +7582,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7925,7 +7916,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -9261,7 +9252,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -9929,7 +9920,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -10263,7 +10254,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -11265,7 +11256,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -12334,7 +12325,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12602,10 +12593,10 @@
         </is>
       </c>
       <c r="H176" s="5" t="n">
-        <v>10160000</v>
+        <v>10211000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>21525</v>
+        <v>21633</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -12613,10 +12604,10 @@
         </is>
       </c>
       <c r="K176" s="5" t="n">
-        <v>8636000</v>
+        <v>8679350</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>18297</v>
+        <v>18388</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -12660,7 +12651,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12928,10 +12919,10 @@
         </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>10140000</v>
+        <v>10191000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>21483</v>
+        <v>21591</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -12939,10 +12930,10 @@
         </is>
       </c>
       <c r="K181" s="5" t="n">
-        <v>8619000</v>
+        <v>8662350</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>18261</v>
+        <v>18352</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -12986,7 +12977,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -13902,7 +13893,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -14232,10 +14223,10 @@
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>10059000</v>
+        <v>10109000</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>21311</v>
+        <v>21417</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -14243,10 +14234,10 @@
         </is>
       </c>
       <c r="K201" s="5" t="n">
-        <v>8550150</v>
+        <v>8592650</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>18115</v>
+        <v>18205</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
@@ -14558,10 +14549,10 @@
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>10039000</v>
+        <v>10089000</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>21269</v>
+        <v>21375</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
@@ -14569,10 +14560,10 @@
         </is>
       </c>
       <c r="K206" s="5" t="n">
-        <v>8533150</v>
+        <v>8575650</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>18079</v>
+        <v>18169</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
@@ -16184,7 +16175,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -17162,7 +17153,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -17488,7 +17479,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -17809,7 +17800,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -17818,10 +17809,10 @@
         </is>
       </c>
       <c r="H256" s="5" t="n">
-        <v>9821000</v>
+        <v>9919000</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>20807</v>
+        <v>21015</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
@@ -17829,10 +17820,10 @@
         </is>
       </c>
       <c r="K256" s="5" t="n">
-        <v>8347850</v>
+        <v>8431150</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>17686</v>
+        <v>17863</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
@@ -26299,7 +26290,7 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -26431,7 +26422,7 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
@@ -26441,12 +26432,12 @@
       </c>
       <c r="H381" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I381" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J381" s="3" t="inlineStr">
@@ -26456,12 +26447,12 @@
       </c>
       <c r="K381" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L381" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M381" s="3" t="inlineStr">
@@ -26471,7 +26462,7 @@
       </c>
       <c r="N381" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26703,7 +26694,7 @@
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -26835,7 +26826,7 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -26845,12 +26836,12 @@
       </c>
       <c r="H387" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I387" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J387" s="3" t="inlineStr">
@@ -26860,12 +26851,12 @@
       </c>
       <c r="K387" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L387" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M387" s="3" t="inlineStr">
@@ -26875,7 +26866,7 @@
       </c>
       <c r="N387" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27107,7 +27098,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -27239,7 +27230,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -27249,12 +27240,12 @@
       </c>
       <c r="H393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J393" s="3" t="inlineStr">
@@ -27264,12 +27255,12 @@
       </c>
       <c r="K393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M393" s="3" t="inlineStr">
@@ -27279,7 +27270,7 @@
       </c>
       <c r="N393" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27511,7 +27502,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -27643,7 +27634,7 @@
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G399" s="3" t="inlineStr">
@@ -27653,12 +27644,12 @@
       </c>
       <c r="H399" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I399" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J399" s="3" t="inlineStr">
@@ -27668,12 +27659,12 @@
       </c>
       <c r="K399" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L399" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M399" s="3" t="inlineStr">
@@ -27683,7 +27674,7 @@
       </c>
       <c r="N399" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27915,7 +27906,7 @@
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
@@ -28047,7 +28038,7 @@
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G405" s="3" t="inlineStr">
@@ -28057,12 +28048,12 @@
       </c>
       <c r="H405" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I405" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J405" s="3" t="inlineStr">
@@ -28072,12 +28063,12 @@
       </c>
       <c r="K405" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L405" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M405" s="3" t="inlineStr">
@@ -28087,7 +28078,7 @@
       </c>
       <c r="N405" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28319,7 +28310,7 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -28451,7 +28442,7 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -28461,12 +28452,12 @@
       </c>
       <c r="H411" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I411" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J411" s="3" t="inlineStr">
@@ -28476,12 +28467,12 @@
       </c>
       <c r="K411" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L411" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M411" s="3" t="inlineStr">
@@ -28491,7 +28482,7 @@
       </c>
       <c r="N411" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28723,7 +28714,7 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -28855,7 +28846,7 @@
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -28865,12 +28856,12 @@
       </c>
       <c r="H417" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I417" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J417" s="3" t="inlineStr">
@@ -28880,12 +28871,12 @@
       </c>
       <c r="K417" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L417" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M417" s="3" t="inlineStr">
@@ -28895,7 +28886,7 @@
       </c>
       <c r="N417" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29118,7 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -29259,7 +29250,7 @@
       </c>
       <c r="F423" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
@@ -29269,12 +29260,12 @@
       </c>
       <c r="H423" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I423" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J423" s="3" t="inlineStr">
@@ -29284,12 +29275,12 @@
       </c>
       <c r="K423" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L423" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M423" s="3" t="inlineStr">
@@ -29299,7 +29290,7 @@
       </c>
       <c r="N423" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -29531,7 +29522,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -29663,7 +29654,7 @@
       </c>
       <c r="F429" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G429" s="3" t="inlineStr">
@@ -29673,12 +29664,12 @@
       </c>
       <c r="H429" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I429" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J429" s="3" t="inlineStr">
@@ -29688,12 +29679,12 @@
       </c>
       <c r="K429" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L429" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M429" s="3" t="inlineStr">
@@ -29703,7 +29694,7 @@
       </c>
       <c r="N429" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -29935,7 +29926,7 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -30067,7 +30058,7 @@
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G435" s="3" t="inlineStr">
@@ -30077,12 +30068,12 @@
       </c>
       <c r="H435" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I435" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J435" s="3" t="inlineStr">
@@ -30092,12 +30083,12 @@
       </c>
       <c r="K435" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L435" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M435" s="3" t="inlineStr">
@@ -30107,7 +30098,7 @@
       </c>
       <c r="N435" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30335,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -30471,7 +30462,7 @@
       </c>
       <c r="F441" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G441" s="3" t="inlineStr">
@@ -30481,12 +30472,12 @@
       </c>
       <c r="H441" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I441" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J441" s="3" t="inlineStr">
@@ -30496,12 +30487,12 @@
       </c>
       <c r="K441" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L441" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M441" s="3" t="inlineStr">
@@ -30511,7 +30502,7 @@
       </c>
       <c r="N441" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30866,7 @@
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
@@ -30885,12 +30876,12 @@
       </c>
       <c r="H447" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I447" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J447" s="3" t="inlineStr">
@@ -30900,12 +30891,12 @@
       </c>
       <c r="K447" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L447" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M447" s="3" t="inlineStr">
@@ -30915,7 +30906,7 @@
       </c>
       <c r="N447" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31279,7 +31270,7 @@
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G453" s="3" t="inlineStr">
@@ -31289,12 +31280,12 @@
       </c>
       <c r="H453" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I453" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J453" s="3" t="inlineStr">
@@ -31304,12 +31295,12 @@
       </c>
       <c r="K453" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L453" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M453" s="3" t="inlineStr">
@@ -31319,7 +31310,7 @@
       </c>
       <c r="N453" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31674,7 @@
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G459" s="3" t="inlineStr">
@@ -31693,12 +31684,12 @@
       </c>
       <c r="H459" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I459" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J459" s="3" t="inlineStr">
@@ -31708,12 +31699,12 @@
       </c>
       <c r="K459" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L459" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M459" s="3" t="inlineStr">
@@ -31723,7 +31714,7 @@
       </c>
       <c r="N459" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32087,7 +32078,7 @@
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G465" s="3" t="inlineStr">
@@ -32097,12 +32088,12 @@
       </c>
       <c r="H465" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I465" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J465" s="3" t="inlineStr">
@@ -32112,12 +32103,12 @@
       </c>
       <c r="K465" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L465" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M465" s="3" t="inlineStr">
@@ -32127,7 +32118,7 @@
       </c>
       <c r="N465" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32496,7 +32487,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -35122,7 +35113,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -37142,7 +37133,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -38758,7 +38749,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -40778,7 +40769,7 @@
       </c>
       <c r="G594" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H594" s="5" t="n">
@@ -41186,10 +41177,10 @@
         </is>
       </c>
       <c r="H600" s="5" t="n">
-        <v>8466000</v>
+        <v>8551000</v>
       </c>
       <c r="I600" s="5" t="n">
-        <v>18689</v>
+        <v>18876</v>
       </c>
       <c r="J600" s="3" t="inlineStr">
         <is>
@@ -41197,10 +41188,10 @@
         </is>
       </c>
       <c r="K600" s="5" t="n">
-        <v>7196100</v>
+        <v>7268350</v>
       </c>
       <c r="L600" s="5" t="n">
-        <v>15885</v>
+        <v>16045</v>
       </c>
       <c r="M600" s="3" t="inlineStr">
         <is>
@@ -41590,10 +41581,10 @@
         </is>
       </c>
       <c r="H606" s="5" t="n">
-        <v>8432000</v>
+        <v>8516000</v>
       </c>
       <c r="I606" s="5" t="n">
-        <v>18614</v>
+        <v>18799</v>
       </c>
       <c r="J606" s="3" t="inlineStr">
         <is>
@@ -41601,10 +41592,10 @@
         </is>
       </c>
       <c r="K606" s="5" t="n">
-        <v>7167200</v>
+        <v>7238600</v>
       </c>
       <c r="L606" s="5" t="n">
-        <v>15822</v>
+        <v>15979</v>
       </c>
       <c r="M606" s="3" t="inlineStr">
         <is>
@@ -47865,7 +47856,7 @@
       </c>
       <c r="F696" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G696" s="3" t="inlineStr">
@@ -47989,7 +47980,7 @@
       </c>
       <c r="F698" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G698" s="3" t="inlineStr">
@@ -48191,34 +48182,34 @@
       </c>
       <c r="F701" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G701" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H701" s="5" t="n">
-        <v>8833000</v>
+        <v>7508000</v>
       </c>
       <c r="I701" s="5" t="n">
-        <v>19037</v>
+        <v>16181</v>
       </c>
       <c r="J701" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K701" s="5" t="n">
-        <v>7508050</v>
+        <v>7508000</v>
       </c>
       <c r="L701" s="5" t="n">
         <v>16181</v>
       </c>
       <c r="M701" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N701" s="3" t="inlineStr">
@@ -48253,7 +48244,7 @@
       </c>
       <c r="F702" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G702" s="3" t="inlineStr">
@@ -48315,7 +48306,7 @@
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G703" s="3" t="inlineStr">
@@ -48517,7 +48508,7 @@
       </c>
       <c r="F706" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G706" s="3" t="inlineStr">
@@ -48579,7 +48570,7 @@
       </c>
       <c r="F707" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G707" s="3" t="inlineStr">
@@ -48641,7 +48632,7 @@
       </c>
       <c r="F708" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G708" s="3" t="inlineStr">
@@ -48843,7 +48834,7 @@
       </c>
       <c r="F711" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G711" s="3" t="inlineStr">
@@ -48905,7 +48896,7 @@
       </c>
       <c r="F712" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G712" s="3" t="inlineStr">
@@ -48967,7 +48958,7 @@
       </c>
       <c r="F713" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G713" s="3" t="inlineStr">
@@ -49169,7 +49160,7 @@
       </c>
       <c r="F716" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G716" s="3" t="inlineStr">
@@ -49231,7 +49222,7 @@
       </c>
       <c r="F717" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G717" s="3" t="inlineStr">
@@ -49293,7 +49284,7 @@
       </c>
       <c r="F718" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G718" s="3" t="inlineStr">
@@ -49557,7 +49548,7 @@
       </c>
       <c r="F722" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G722" s="3" t="inlineStr">
@@ -49619,7 +49610,7 @@
       </c>
       <c r="F723" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G723" s="3" t="inlineStr">
@@ -49883,7 +49874,7 @@
       </c>
       <c r="F727" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G727" s="3" t="inlineStr">
@@ -49945,7 +49936,7 @@
       </c>
       <c r="F728" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G728" s="3" t="inlineStr">
@@ -50209,7 +50200,7 @@
       </c>
       <c r="F732" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G732" s="3" t="inlineStr">
@@ -50271,7 +50262,7 @@
       </c>
       <c r="F733" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G733" s="3" t="inlineStr">
@@ -50535,7 +50526,7 @@
       </c>
       <c r="F737" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G737" s="3" t="inlineStr">
@@ -50597,7 +50588,7 @@
       </c>
       <c r="F738" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G738" s="3" t="inlineStr">
@@ -50804,7 +50795,7 @@
       </c>
       <c r="G741" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H741" s="5" t="n">
@@ -50861,7 +50852,7 @@
       </c>
       <c r="F742" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G742" s="3" t="inlineStr">
@@ -50923,7 +50914,7 @@
       </c>
       <c r="F743" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G743" s="3" t="inlineStr">
@@ -51130,7 +51121,7 @@
       </c>
       <c r="G746" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H746" s="5" t="n">
@@ -51187,7 +51178,7 @@
       </c>
       <c r="F747" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G747" s="3" t="inlineStr">
@@ -51580,7 +51571,7 @@
       </c>
       <c r="G753" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H753" s="5" t="n">
@@ -51844,7 +51835,7 @@
       </c>
       <c r="G757" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H757" s="5" t="n">
@@ -52822,7 +52813,7 @@
       </c>
       <c r="G772" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H772" s="5" t="n">
@@ -53148,7 +53139,7 @@
       </c>
       <c r="G777" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H777" s="5" t="n">
@@ -59310,7 +59301,7 @@
       </c>
       <c r="G872" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H872" s="5" t="n">
@@ -59574,7 +59565,7 @@
       </c>
       <c r="G876" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H876" s="5" t="n">
@@ -61317,7 +61308,7 @@
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G902" s="3" t="inlineStr">
@@ -61326,10 +61317,10 @@
         </is>
       </c>
       <c r="H902" s="5" t="n">
-        <v>9139000</v>
+        <v>9080000</v>
       </c>
       <c r="I902" s="5" t="n">
-        <v>19911</v>
+        <v>19782</v>
       </c>
       <c r="J902" s="3" t="inlineStr">
         <is>
@@ -61337,10 +61328,10 @@
         </is>
       </c>
       <c r="K902" s="5" t="n">
-        <v>7768150</v>
+        <v>7718000</v>
       </c>
       <c r="L902" s="5" t="n">
-        <v>16924</v>
+        <v>16815</v>
       </c>
       <c r="M902" s="3" t="inlineStr">
         <is>
@@ -61799,7 +61790,7 @@
       </c>
       <c r="F909" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G909" s="3" t="inlineStr">
@@ -61808,10 +61799,10 @@
         </is>
       </c>
       <c r="H909" s="5" t="n">
-        <v>9121000</v>
+        <v>9062000</v>
       </c>
       <c r="I909" s="5" t="n">
-        <v>19871</v>
+        <v>19743</v>
       </c>
       <c r="J909" s="3" t="inlineStr">
         <is>
@@ -61819,10 +61810,10 @@
         </is>
       </c>
       <c r="K909" s="5" t="n">
-        <v>7752850</v>
+        <v>7702700</v>
       </c>
       <c r="L909" s="5" t="n">
-        <v>16891</v>
+        <v>16781</v>
       </c>
       <c r="M909" s="3" t="inlineStr">
         <is>
@@ -62281,7 +62272,7 @@
       </c>
       <c r="F916" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G916" s="3" t="inlineStr">
@@ -62763,7 +62754,7 @@
       </c>
       <c r="F923" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G923" s="3" t="inlineStr">
@@ -63245,7 +63236,7 @@
       </c>
       <c r="F930" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G930" s="3" t="inlineStr">
@@ -63727,7 +63718,7 @@
       </c>
       <c r="F937" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G937" s="3" t="inlineStr">
@@ -64209,7 +64200,7 @@
       </c>
       <c r="F944" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G944" s="3" t="inlineStr">
@@ -64691,7 +64682,7 @@
       </c>
       <c r="F951" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G951" s="3" t="inlineStr">
@@ -65173,7 +65164,7 @@
       </c>
       <c r="F958" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G958" s="3" t="inlineStr">
@@ -65655,7 +65646,7 @@
       </c>
       <c r="F965" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G965" s="3" t="inlineStr">
@@ -66137,7 +66128,7 @@
       </c>
       <c r="F972" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G972" s="3" t="inlineStr">
@@ -66619,7 +66610,7 @@
       </c>
       <c r="F979" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G979" s="3" t="inlineStr">
@@ -67101,7 +67092,7 @@
       </c>
       <c r="F986" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G986" s="3" t="inlineStr">
@@ -67583,7 +67574,7 @@
       </c>
       <c r="F993" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G993" s="3" t="inlineStr">
@@ -68065,7 +68056,7 @@
       </c>
       <c r="F1000" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1000" s="3" t="inlineStr">
@@ -72883,7 +72874,7 @@
       </c>
       <c r="F1071" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1071" s="3" t="inlineStr">
@@ -73357,7 +73348,7 @@
       </c>
       <c r="F1078" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1078" s="3" t="inlineStr">
@@ -73831,7 +73822,7 @@
       </c>
       <c r="F1085" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1085" s="3" t="inlineStr">
@@ -74297,7 +74288,7 @@
       </c>
       <c r="F1092" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1092" s="3" t="inlineStr">
@@ -74755,7 +74746,7 @@
       </c>
       <c r="F1099" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1099" s="3" t="inlineStr">
@@ -75972,7 +75963,7 @@
       </c>
       <c r="G1117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H1117" s="5" t="n">
@@ -77551,7 +77542,7 @@
       </c>
       <c r="F1141" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1141" s="3" t="inlineStr">
@@ -78017,7 +78008,7 @@
       </c>
       <c r="F1148" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1148" s="3" t="inlineStr">
@@ -78949,34 +78940,34 @@
       </c>
       <c r="F1162" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H1162" s="5" t="n">
-        <v>7004000</v>
+        <v>6093400</v>
       </c>
       <c r="I1162" s="5" t="n">
-        <v>20184</v>
+        <v>17560</v>
       </c>
       <c r="J1162" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1162" s="5" t="n">
-        <v>5953400</v>
+        <v>6093400</v>
       </c>
       <c r="L1162" s="5" t="n">
-        <v>17157</v>
+        <v>17560</v>
       </c>
       <c r="M1162" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1162" s="3" t="inlineStr">
@@ -79415,34 +79406,34 @@
       </c>
       <c r="F1169" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H1169" s="5" t="n">
-        <v>6993000</v>
+        <v>5944000</v>
       </c>
       <c r="I1169" s="5" t="n">
-        <v>20153</v>
+        <v>17130</v>
       </c>
       <c r="J1169" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1169" s="5" t="n">
-        <v>5944050</v>
+        <v>5944000</v>
       </c>
       <c r="L1169" s="5" t="n">
         <v>17130</v>
       </c>
       <c r="M1169" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1169" s="3" t="inlineStr">
@@ -79881,7 +79872,7 @@
       </c>
       <c r="F1176" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1176" s="3" t="inlineStr">
@@ -81300,7 +81291,7 @@
       </c>
       <c r="G1197" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H1197" s="5" t="n">
@@ -83867,7 +83858,7 @@
       </c>
       <c r="F1235" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1235" s="3" t="inlineStr">
@@ -83937,7 +83928,7 @@
       </c>
       <c r="F1236" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1236" s="3" t="inlineStr">
@@ -84341,7 +84332,7 @@
       </c>
       <c r="F1242" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1242" s="3" t="inlineStr">
@@ -84411,7 +84402,7 @@
       </c>
       <c r="F1243" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1243" s="3" t="inlineStr">
@@ -85763,7 +85754,7 @@
       </c>
       <c r="F1263" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1263" s="3" t="inlineStr">
@@ -85833,7 +85824,7 @@
       </c>
       <c r="F1264" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1264" s="3" t="inlineStr">
@@ -86035,7 +86026,7 @@
       </c>
       <c r="F1267" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G1267" s="3" t="inlineStr">
@@ -86237,7 +86228,7 @@
       </c>
       <c r="F1270" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1270" s="3" t="inlineStr">
@@ -86307,7 +86298,7 @@
       </c>
       <c r="F1271" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1271" s="3" t="inlineStr">
@@ -86514,7 +86505,7 @@
       </c>
       <c r="G1274" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H1274" s="5" t="n">
@@ -86711,7 +86702,7 @@
       </c>
       <c r="F1277" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1277" s="3" t="inlineStr">
@@ -86781,7 +86772,7 @@
       </c>
       <c r="F1278" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1278" s="3" t="inlineStr">
@@ -87458,12 +87449,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -88289,12 +88280,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$872万
-$19,552/呎
-(在售)</t>
+$881万
+$19,747/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -88336,7 +88327,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $740万
@@ -88359,12 +88350,12 @@
           <t>49</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1049万
 $22,222/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -88383,12 +88374,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$869万
-$19,491/呎
-(在售)</t>
+$878万
+$19,686/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -88406,12 +88397,12 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1049万
 $22,222/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -88430,7 +88421,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $739万
@@ -88453,12 +88444,12 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1045万
 $22,136/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -88477,7 +88468,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $737万
@@ -88524,7 +88515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $728万
@@ -88571,7 +88562,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $727万
@@ -88618,7 +88609,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $733万
@@ -88641,12 +88632,12 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1036万
 $21,960/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -88665,7 +88656,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $725万
@@ -88688,7 +88679,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $879万
@@ -88712,7 +88703,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $724万
@@ -88735,12 +88726,12 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1032万
 $21,873/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -88759,7 +88750,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $723万
@@ -88782,12 +88773,12 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1030万
 $21,826/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -88806,7 +88797,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $722万
@@ -88853,7 +88844,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $722万
@@ -88900,7 +88891,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $720万
@@ -88923,12 +88914,12 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $1024万
 $21,697/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -88947,7 +88938,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $719万
@@ -88970,7 +88961,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $889万
@@ -88994,7 +88985,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $734万
@@ -89017,7 +89008,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $867万
@@ -89041,7 +89032,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $716万
@@ -89064,7 +89055,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $865万
@@ -89088,7 +89079,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $732万
@@ -89114,8 +89105,8 @@
       <c r="B39" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1016万
-$21,525/呎
+$1021万
+$21,633/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -89135,7 +89126,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $714万
@@ -89143,12 +89134,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F39" s="24" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $755万
 $16,422/呎
-(26年-08月-28日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -89161,8 +89152,8 @@
       <c r="B40" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1014万
-$21,483/呎
+$1019万
+$21,591/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -89182,7 +89173,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $730万
@@ -89190,12 +89181,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F40" s="24" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $754万
 $16,388/呎
-(26年-08月-30日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -89205,7 +89196,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $880万
@@ -89229,7 +89220,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $712万
@@ -89237,7 +89228,54 @@
 (26年-08月-13日)</t>
         </is>
       </c>
-      <c r="F41" s="24" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>E | 460呎 (2房)
+$770万
+$16,742/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>A | 472呎 (2房)
+$880万
+$18,651/呎
+(26年-08月-28日)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 474呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>D | 446呎 (2房)
+$712万
+$15,967/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $770万
@@ -89246,65 +89284,18 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>A | 472呎 (2房)
-$880万
-$18,651/呎
-(26年-08月-28日)</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="inlineStr">
-        <is>
-          <t>B | 567呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr">
-        <is>
-          <t>C | 474呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>D | 446呎 (2房)
-$712万
-$15,967/呎
-(26年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>E | 460呎 (2房)
-$770万
-$16,742/呎
-(26年-08月-28日)</t>
-        </is>
-      </c>
-    </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $857万
 $18,151/呎
-(26年-08月-30日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -89323,7 +89314,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $710万
@@ -89331,7 +89322,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F43" s="24" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $767万
@@ -89349,8 +89340,8 @@
       <c r="B44" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1006万
-$21,311/呎
+$1011万
+$21,417/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -89370,7 +89361,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $726万
@@ -89378,7 +89369,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F44" s="24" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $741万
@@ -89396,8 +89387,8 @@
       <c r="B45" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1004万
-$21,269/呎
+$1009万
+$21,375/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -89417,7 +89408,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $725万
@@ -89425,7 +89416,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F45" s="24" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $739万
@@ -89440,7 +89431,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $850万
@@ -89464,7 +89455,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E46" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $706万
@@ -89472,7 +89463,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="F46" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $736万
@@ -89487,7 +89478,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B47" s="24" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $868万
@@ -89511,7 +89502,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $705万
@@ -89519,7 +89510,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F47" s="24" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $735万
@@ -89534,7 +89525,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $847万
@@ -89558,7 +89549,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="E48" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $704万
@@ -89566,7 +89557,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="F48" s="24" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $733万
@@ -89581,7 +89572,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $845万
@@ -89605,7 +89596,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E49" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $703万
@@ -89613,7 +89604,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F49" s="24" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $732万
@@ -89628,12 +89619,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $845万
 $17,899/呎
-(26年-08月-28日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
@@ -89652,7 +89643,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $719万
@@ -89660,7 +89651,7 @@
 (26年-08月-13日)</t>
         </is>
       </c>
-      <c r="F50" s="24" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $749万
@@ -89675,7 +89666,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B51" s="24" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $842万
@@ -89699,7 +89690,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $717万
@@ -89707,7 +89698,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F51" s="24" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $729万
@@ -89722,7 +89713,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $840万
@@ -89746,7 +89737,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E52" s="24" t="inlineStr">
+      <c r="E52" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $699万
@@ -89754,7 +89745,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F52" s="24" t="inlineStr">
+      <c r="F52" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $744万
@@ -89769,12 +89760,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B53" s="24" t="inlineStr">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $838万
 $17,756/呎
-(26年-08月-28日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
@@ -89793,7 +89784,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E53" s="24" t="inlineStr">
+      <c r="E53" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $698万
@@ -89801,7 +89792,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F53" s="24" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $726万
@@ -89816,12 +89807,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
 $836万
 $17,720/呎
-(26年-08月-28日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
@@ -89840,7 +89831,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E54" s="24" t="inlineStr">
+      <c r="E54" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $714万
@@ -89848,7 +89839,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="F54" s="24" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $724万
@@ -89863,12 +89854,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B55" s="23" t="inlineStr">
+      <c r="B55" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$982万
-$20,807/呎
-(在售)</t>
+$992万
+$21,015/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -89887,7 +89878,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $696万
@@ -89895,7 +89886,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F55" s="24" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $723万
@@ -89934,7 +89925,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E56" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $712万
@@ -89942,7 +89933,7 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="F56" s="24" t="inlineStr">
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $738万
@@ -89981,7 +89972,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="E57" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $694万
@@ -89989,7 +89980,7 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="F57" s="24" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $720万
@@ -90028,7 +90019,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E58" s="24" t="inlineStr">
+      <c r="E58" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $694万
@@ -90036,7 +90027,7 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="F58" s="24" t="inlineStr">
+      <c r="F58" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $720万
@@ -90075,7 +90066,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E59" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $699万
@@ -90083,7 +90074,7 @@
 (26年-08月-30日)</t>
         </is>
       </c>
-      <c r="F59" s="24" t="inlineStr">
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $724万
@@ -90213,12 +90204,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -90233,7 +90224,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
     </row>
@@ -91161,28 +91152,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1078万
 $19,458/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -91216,28 +91207,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1076万
 $19,430/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -91271,28 +91262,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1075万
 $19,399/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -91326,28 +91317,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1075万
 $19,399/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -91381,28 +91372,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1072万
 $19,341/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -91436,28 +91427,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1070万
 $19,312/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -91491,28 +91482,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1068万
 $19,285/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -91546,28 +91537,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1067万
 $19,255/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -91601,28 +91592,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1065万
 $19,226/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -91656,28 +91647,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $1064万
 $19,197/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -91711,28 +91702,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $903万
 $16,293/呎
-(26年-08月-28日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -91766,23 +91757,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $901万
@@ -91821,23 +91812,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $901万
@@ -91876,23 +91867,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $899万
@@ -91931,23 +91922,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 449呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>C | 449呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $893万
@@ -91986,12 +91977,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 $1254万
 $19,976/呎
-(26年-08月-31日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -92002,7 +91993,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $896万
@@ -92041,7 +92032,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92057,7 +92048,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $890万
@@ -92096,7 +92087,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92112,7 +92103,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $889万
@@ -92151,7 +92142,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92167,7 +92158,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $908万
@@ -92206,7 +92197,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92222,7 +92213,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $886万
@@ -92261,7 +92252,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92277,7 +92268,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $885万
@@ -92316,7 +92307,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92332,7 +92323,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $906万
@@ -92371,7 +92362,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92387,7 +92378,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $882万
@@ -92395,12 +92386,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F43" s="24" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $742万
 $16,370/呎
-(26年-08月-28日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G43" s="20" t="inlineStr">
@@ -92426,7 +92417,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92442,7 +92433,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $881万
@@ -92450,7 +92441,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F44" s="24" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $757万
@@ -92481,7 +92472,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="24" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92497,7 +92488,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $900万
@@ -92505,7 +92496,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F45" s="24" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $756万
@@ -92552,7 +92543,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E46" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $897万
@@ -92560,7 +92551,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="F46" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $753万
@@ -92607,7 +92598,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $876万
@@ -92615,7 +92606,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F47" s="24" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $751万
@@ -92662,7 +92653,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="E48" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $895万
@@ -92670,12 +92661,12 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="F48" s="24" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $750万
 $16,555/呎
-(26年-08月-28日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G48" s="20" t="inlineStr">
@@ -92717,7 +92708,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E49" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $873万
@@ -92725,7 +92716,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F49" s="24" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $748万
@@ -92772,7 +92763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $873万
@@ -92780,7 +92771,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F50" s="24" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $748万
@@ -92827,7 +92818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $891万
@@ -92835,7 +92826,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F51" s="24" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $745万
@@ -92882,7 +92873,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E52" s="24" t="inlineStr">
+      <c r="E52" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $869万
@@ -92890,12 +92881,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F52" s="24" t="inlineStr">
+      <c r="F52" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $744万
 $16,422/呎
-(26年-08月-28日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="G52" s="20" t="inlineStr">
@@ -92937,7 +92928,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E53" s="24" t="inlineStr">
+      <c r="E53" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $868万
@@ -92945,7 +92936,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F53" s="24" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $742万
@@ -92992,7 +92983,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E54" s="24" t="inlineStr">
+      <c r="E54" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $866万
@@ -93000,7 +92991,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F54" s="24" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $741万
@@ -93047,7 +93038,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $865万
@@ -93055,7 +93046,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="F55" s="24" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $740万
@@ -93102,7 +93093,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E56" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $864万
@@ -93110,7 +93101,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F56" s="24" t="inlineStr">
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $721万
@@ -93157,7 +93148,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="E57" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $883万
@@ -93165,12 +93156,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F57" s="24" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $737万
 $16,259/呎
-(26年-08月-29日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G57" s="20" t="inlineStr">
@@ -93212,7 +93203,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E58" s="24" t="inlineStr">
+      <c r="E58" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $887万
@@ -93223,8 +93214,8 @@
       <c r="F58" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$847万
-$18,689/呎
+$855万
+$18,876/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -93267,7 +93258,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E59" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
 $880万
@@ -93278,8 +93269,8 @@
       <c r="F59" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$843万
-$18,614/呎
+$852万
+$18,799/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -93420,17 +93411,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -93530,7 +93521,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93577,7 +93568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93624,7 +93615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93671,7 +93662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93718,7 +93709,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93765,7 +93756,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93812,7 +93803,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93859,7 +93850,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93906,7 +93897,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93953,7 +93944,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94000,7 +93991,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94047,7 +94038,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94094,7 +94085,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94141,7 +94132,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94188,7 +94179,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94235,7 +94226,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94243,15 +94234,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $929万
 $19,045/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $732万
@@ -94259,12 +94250,12 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $885万
 $19,065/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -94282,7 +94273,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94290,28 +94281,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $928万
 $19,006/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $869万
 $19,521/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
-$883万
-$19,037/呎
-(在售)</t>
+$751万
+$16,181/呎
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -94329,7 +94320,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94337,28 +94328,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $926万
 $18,967/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $867万
 $19,492/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $882万
 $19,009/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -94376,7 +94367,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94384,28 +94375,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $926万
 $18,967/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $867万
 $19,492/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $882万
 $19,009/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -94423,7 +94414,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94431,28 +94422,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $922万
 $18,893/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $865万
 $19,434/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $879万
 $18,950/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -94470,7 +94461,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94478,23 +94469,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $920万
 $18,855/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $864万
 $19,404/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $746万
@@ -94517,7 +94508,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94525,23 +94516,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $918万
 $18,820/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $862万
 $19,375/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $745万
@@ -94564,7 +94555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94572,23 +94563,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $916万
 $18,781/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $861万
 $19,346/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $744万
@@ -94611,7 +94602,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94619,23 +94610,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $915万
 $18,742/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $860万
 $19,317/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F29" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $743万
@@ -94658,7 +94649,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94666,28 +94657,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $913万
 $18,705/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $858万
 $19,290/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $759万
 $16,363/呎
-(26年-08月-27日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -94705,7 +94696,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94713,7 +94704,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $774万
@@ -94721,20 +94712,20 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $857万
 $19,261/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F31" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $741万
 $15,963/呎
-(26年-08月-26日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -94752,7 +94743,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94760,15 +94751,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $773万
 $15,836/呎
-(26年-08月-28日)</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $745万
@@ -94776,7 +94767,7 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F32" s="24" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $740万
@@ -94799,7 +94790,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94807,7 +94798,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $909万
@@ -94815,15 +94806,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $727万
 $16,347/呎
-(26年-08月-31日)</t>
-        </is>
-      </c>
-      <c r="F33" s="24" t="inlineStr">
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $740万
@@ -94846,7 +94837,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94854,7 +94845,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $788万
@@ -94862,7 +94853,7 @@
 (26年-08月-31日)</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $725万
@@ -94870,7 +94861,7 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $755万
@@ -94893,7 +94884,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94901,7 +94892,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $768万
@@ -94909,7 +94900,7 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $724万
@@ -94917,7 +94908,7 @@
 (26年-08月-30日)</t>
         </is>
       </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $736万
@@ -94940,7 +94931,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94948,7 +94939,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $759万
@@ -94956,15 +94947,15 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $740万
 $16,631/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $752万
@@ -94987,7 +94978,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94995,7 +94986,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $758万
@@ -95003,15 +94994,15 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $739万
 $16,606/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $727万
@@ -95034,7 +95025,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95042,7 +95033,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $756万
@@ -95050,7 +95041,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $714万
@@ -95058,7 +95049,7 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="F38" s="24" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $726万
@@ -95081,7 +95072,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 $1101万
@@ -95089,7 +95080,7 @@
 (26年-09月-08日)</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $754万
@@ -95097,7 +95088,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $713万
@@ -95105,7 +95096,7 @@
 (26年-09月-10日)</t>
         </is>
       </c>
-      <c r="F39" s="24" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $725万
@@ -95128,7 +95119,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 $1099万
@@ -95136,7 +95127,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $771万
@@ -95144,7 +95135,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $712万
@@ -95152,7 +95143,7 @@
 (26年-08月-26日)</t>
         </is>
       </c>
-      <c r="F40" s="24" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $724万
@@ -95175,7 +95166,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95183,7 +95174,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $751万
@@ -95191,7 +95182,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $727万
@@ -95199,7 +95190,7 @@
 (26年-09月-08日)</t>
         </is>
       </c>
-      <c r="F41" s="24" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $722万
@@ -95222,7 +95213,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95230,7 +95221,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $751万
@@ -95238,7 +95229,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $711万
@@ -95246,7 +95237,7 @@
 (26年-09月-08日)</t>
         </is>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $722万
@@ -95269,7 +95260,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95277,7 +95268,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D43" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $749万
@@ -95285,7 +95276,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $708万
@@ -95293,7 +95284,7 @@
 (26年-09月-10日)</t>
         </is>
       </c>
-      <c r="F43" s="24" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $720万
@@ -95316,7 +95307,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 $1090万
@@ -95324,7 +95315,7 @@
 (26年-08月-31日)</t>
         </is>
       </c>
-      <c r="D44" s="24" t="inlineStr">
+      <c r="D44" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $765万
@@ -95332,7 +95323,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $707万
@@ -95340,7 +95331,7 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="F44" s="24" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $719万
@@ -95363,7 +95354,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 $1116万
@@ -95371,7 +95362,7 @@
 (26年-08月-26日)</t>
         </is>
       </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="D45" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $746万
@@ -95379,7 +95370,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $723万
@@ -95387,7 +95378,7 @@
 (26年-09月-04日)</t>
         </is>
       </c>
-      <c r="F45" s="24" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $718万
@@ -95410,7 +95401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95418,7 +95409,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D46" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $743万
@@ -95426,7 +95417,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E46" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $721万
@@ -95434,7 +95425,7 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="F46" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $716万
@@ -95465,7 +95456,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="D47" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $741万
@@ -95473,7 +95464,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $703万
@@ -95481,7 +95472,7 @@
 (26年-08月-27日)</t>
         </is>
       </c>
-      <c r="F47" s="24" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $715万
@@ -95512,7 +95503,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D48" s="24" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $740万
@@ -95520,7 +95511,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="E48" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $719万
@@ -95528,7 +95519,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="F48" s="24" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $714万
@@ -95559,7 +95550,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D49" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $738万
@@ -95567,7 +95558,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E49" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $717万
@@ -95575,7 +95566,7 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="F49" s="24" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $737万
@@ -95606,7 +95597,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D50" s="24" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $738万
@@ -95614,7 +95605,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $701万
@@ -95622,7 +95613,7 @@
 (26年-09月-10日)</t>
         </is>
       </c>
-      <c r="F50" s="24" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $720万
@@ -95653,7 +95644,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="D51" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $735万
@@ -95661,7 +95652,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $715万
@@ -95669,7 +95660,7 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="F51" s="24" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $711万
@@ -95700,7 +95691,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $734万
@@ -95708,7 +95699,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="E52" s="24" t="inlineStr">
+      <c r="E52" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $698万
@@ -95716,7 +95707,7 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="F52" s="24" t="inlineStr">
+      <c r="F52" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $726万
@@ -95747,7 +95738,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D53" s="24" t="inlineStr">
+      <c r="D53" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $732万
@@ -95755,7 +95746,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="E53" s="24" t="inlineStr">
+      <c r="E53" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $713万
@@ -95763,7 +95754,7 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="F53" s="24" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $716万
@@ -95794,7 +95785,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D54" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $731万
@@ -95802,7 +95793,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="E54" s="24" t="inlineStr">
+      <c r="E54" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $712万
@@ -95810,7 +95801,7 @@
 (26年-09月-14日)</t>
         </is>
       </c>
-      <c r="F54" s="24" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $708万
@@ -95841,7 +95832,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="D55" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $746万
@@ -95849,7 +95840,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $711万
@@ -95857,7 +95848,7 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="F55" s="24" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $713万
@@ -95888,7 +95879,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D56" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $745万
@@ -95896,15 +95887,15 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E56" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $701万
 $15,747/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="F56" s="24" t="inlineStr">
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $712万
@@ -95935,7 +95926,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="D57" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $726万
@@ -95943,7 +95934,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="E57" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $709万
@@ -95951,12 +95942,12 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="F57" s="24" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $711万
 $15,329/呎
-(26年-08月-27日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -95982,7 +95973,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D58" s="24" t="inlineStr">
+      <c r="D58" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $726万
@@ -95990,7 +95981,7 @@
 (26年-08月-26日)</t>
         </is>
       </c>
-      <c r="E58" s="24" t="inlineStr">
+      <c r="E58" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $709万
@@ -95998,7 +95989,7 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="F58" s="24" t="inlineStr">
+      <c r="F58" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $728万
@@ -96029,7 +96020,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="D59" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $741万
@@ -96037,7 +96028,7 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E59" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
 $714万
@@ -96045,7 +96036,7 @@
 (26年-09月-01日)</t>
         </is>
       </c>
-      <c r="F59" s="24" t="inlineStr">
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $726万
@@ -96176,22 +96167,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -96312,7 +96303,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96320,7 +96311,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96352,12 +96343,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
-$914万
-$19,911/呎
-(在售)</t>
+$908万
+$19,782/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96375,7 +96366,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96383,7 +96374,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96415,12 +96406,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
-$912万
-$19,871/呎
-(在售)</t>
+$906万
+$19,743/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96438,7 +96429,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96446,7 +96437,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96478,12 +96469,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $904万
 $19,704/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96501,7 +96492,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96509,7 +96500,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96541,12 +96532,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $904万
 $19,704/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96564,7 +96555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96572,7 +96563,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96604,12 +96595,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $901万
 $19,625/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96627,7 +96618,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96635,7 +96626,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96667,12 +96658,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $899万
 $19,584/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96690,7 +96681,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96698,7 +96689,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96730,12 +96721,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $897万
 $19,547/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96753,7 +96744,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96761,7 +96752,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96793,12 +96784,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $895万
 $19,508/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96816,7 +96807,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96824,7 +96815,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96856,12 +96847,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $894万
 $19,468/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96879,7 +96870,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96887,7 +96878,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96919,12 +96910,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $892万
 $19,431/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -96942,7 +96933,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96950,7 +96941,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96982,12 +96973,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $890万
 $19,390/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -97005,7 +96996,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97013,7 +97004,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97045,12 +97036,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $888万
 $19,351/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -97068,7 +97059,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97076,7 +97067,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97108,12 +97099,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $886万
 $19,314/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -97131,7 +97122,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97139,7 +97130,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97171,12 +97162,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H19" s="23" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $885万
 $19,275/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -97194,7 +97185,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97202,7 +97193,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97234,12 +97225,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
 $883万
 $19,235/呎
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -97257,7 +97248,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97265,7 +97256,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97297,7 +97288,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H21" s="24" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $743万
@@ -97320,7 +97311,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97328,7 +97319,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97360,7 +97351,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H22" s="24" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $725万
@@ -97383,7 +97374,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97391,7 +97382,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97423,7 +97414,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $741万
@@ -97446,7 +97437,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1537万
@@ -97454,7 +97445,7 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97486,7 +97477,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H24" s="24" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $724万
@@ -97509,7 +97500,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97517,7 +97508,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97549,7 +97540,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H25" s="24" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $722万
@@ -97572,7 +97563,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97580,7 +97571,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97612,7 +97603,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H26" s="24" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $721万
@@ -97635,7 +97626,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97643,7 +97634,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97675,7 +97666,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H27" s="24" t="inlineStr">
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $720万
@@ -97698,7 +97689,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97706,7 +97697,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97738,7 +97729,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H28" s="24" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $718万
@@ -97761,7 +97752,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97769,7 +97760,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97801,7 +97792,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H29" s="24" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $717万
@@ -97824,7 +97815,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97832,7 +97823,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97856,15 +97847,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $714万
 $20,579/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H30" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $716万
@@ -97887,7 +97878,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97895,7 +97886,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97919,15 +97910,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $713万
 $20,550/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H31" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $715万
@@ -97950,7 +97941,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1510万
@@ -97958,7 +97949,7 @@
 (26年-09月-04日)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97982,15 +97973,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $712万
 $20,519/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H32" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $714万
@@ -98013,7 +98004,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1547万
@@ -98021,7 +98012,7 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $1046万
@@ -98045,15 +98036,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $712万
 $20,519/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H33" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $714万
@@ -98076,7 +98067,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98084,7 +98075,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98108,15 +98099,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $710万
 $20,458/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H34" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $712万
@@ -98139,7 +98130,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1501万
@@ -98147,7 +98138,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98179,7 +98170,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H35" s="24" t="inlineStr">
+      <c r="H35" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $711万
@@ -98202,15 +98193,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1498万
 $19,128/呎
-(26年-08月-31日)</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
+(26年-09月-17日)</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98242,7 +98233,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H36" s="24" t="inlineStr">
+      <c r="H36" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $710万
@@ -98265,7 +98256,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1495万
@@ -98273,7 +98264,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 $1036万
@@ -98305,7 +98296,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H37" s="24" t="inlineStr">
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $709万
@@ -98328,7 +98319,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1492万
@@ -98336,7 +98327,7 @@
 (26年-08月-07日)</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98368,7 +98359,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H38" s="24" t="inlineStr">
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $708万
@@ -98391,7 +98382,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1489万
@@ -98399,7 +98390,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98431,7 +98422,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H39" s="24" t="inlineStr">
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $706万
@@ -98454,7 +98445,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1486万
@@ -98462,7 +98453,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98486,15 +98477,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G40" s="23" t="inlineStr">
+      <c r="G40" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $704万
 $20,274/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H40" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $722万
@@ -98517,7 +98508,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1483万
@@ -98525,7 +98516,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98549,15 +98540,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G41" s="23" t="inlineStr">
+      <c r="G41" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $702万
 $20,245/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $704万
@@ -98580,7 +98571,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1483万
@@ -98588,7 +98579,7 @@
 (26年-09月-07日)</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98612,7 +98603,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G42" s="24" t="inlineStr">
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $597万
@@ -98620,7 +98611,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="H42" s="24" t="inlineStr">
+      <c r="H42" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $704万
@@ -98643,7 +98634,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1477万
@@ -98651,7 +98642,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98678,12 +98669,12 @@
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$700万
-$20,184/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H43" s="24" t="inlineStr">
+$609万
+$17,560/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $719万
@@ -98706,7 +98697,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1474万
@@ -98714,7 +98705,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98741,12 +98732,12 @@
       <c r="G44" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$699万
-$20,153/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H44" s="24" t="inlineStr">
+$594万
+$17,130/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $718万
@@ -98769,7 +98760,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 $1471万
@@ -98777,7 +98768,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D45" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98801,15 +98792,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G45" s="23" t="inlineStr">
+      <c r="G45" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $698万
 $20,121/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H45" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $717万
@@ -98832,7 +98823,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98840,7 +98831,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98864,7 +98855,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G46" s="24" t="inlineStr">
+      <c r="G46" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $606万
@@ -98872,7 +98863,7 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="H46" s="24" t="inlineStr">
+      <c r="H46" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $714万
@@ -98895,7 +98886,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98903,7 +98894,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98927,7 +98918,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G47" s="24" t="inlineStr">
+      <c r="G47" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $591万
@@ -98935,7 +98926,7 @@
 (26年-09月-14日)</t>
         </is>
       </c>
-      <c r="H47" s="24" t="inlineStr">
+      <c r="H47" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $697万
@@ -98958,7 +98949,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98966,7 +98957,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98990,15 +98981,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G48" s="24" t="inlineStr">
+      <c r="G48" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $590万
 $17,002/呎
-(26年-08月-28日)</t>
-        </is>
-      </c>
-      <c r="H48" s="24" t="inlineStr">
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="H48" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $696万
@@ -99021,7 +99012,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99029,7 +99020,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99053,7 +99044,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G49" s="24" t="inlineStr">
+      <c r="G49" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $589万
@@ -99061,7 +99052,7 @@
 (26年-08月-29日)</t>
         </is>
       </c>
-      <c r="H49" s="24" t="inlineStr">
+      <c r="H49" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $695万
@@ -99084,7 +99075,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99092,7 +99083,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99116,7 +99107,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G50" s="24" t="inlineStr">
+      <c r="G50" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $583万
@@ -99124,7 +99115,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="H50" s="24" t="inlineStr">
+      <c r="H50" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $711万
@@ -99147,7 +99138,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99155,7 +99146,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D51" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99179,7 +99170,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G51" s="24" t="inlineStr">
+      <c r="G51" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $581万
@@ -99187,7 +99178,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="H51" s="24" t="inlineStr">
+      <c r="H51" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $709万
@@ -99210,7 +99201,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99218,7 +99209,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99242,7 +99233,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G52" s="24" t="inlineStr">
+      <c r="G52" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $581万
@@ -99250,7 +99241,7 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="H52" s="24" t="inlineStr">
+      <c r="H52" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $708万
@@ -99273,20 +99264,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C53" s="25" t="inlineStr">
+      <c r="C53" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D53" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
@@ -99305,7 +99296,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G53" s="24" t="inlineStr">
+      <c r="G53" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $580万
@@ -99313,7 +99304,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="H53" s="24" t="inlineStr">
+      <c r="H53" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $691万
@@ -99336,20 +99327,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C54" s="25" t="inlineStr">
+      <c r="C54" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
@@ -99368,7 +99359,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G54" s="24" t="inlineStr">
+      <c r="G54" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $579万
@@ -99376,7 +99367,7 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="H54" s="24" t="inlineStr">
+      <c r="H54" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $706万
@@ -99399,7 +99390,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99407,7 +99398,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99431,7 +99422,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G55" s="24" t="inlineStr">
+      <c r="G55" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $578万
@@ -99439,7 +99430,7 @@
 (26年-08月-24日)</t>
         </is>
       </c>
-      <c r="H55" s="24" t="inlineStr">
+      <c r="H55" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $689万
@@ -99462,7 +99453,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99470,7 +99461,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99494,7 +99485,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G56" s="24" t="inlineStr">
+      <c r="G56" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $577万
@@ -99502,7 +99493,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="H56" s="24" t="inlineStr">
+      <c r="H56" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $704万
@@ -99525,20 +99516,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C57" s="25" t="inlineStr">
+      <c r="C57" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D57" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
@@ -99557,7 +99548,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G57" s="24" t="inlineStr">
+      <c r="G57" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $576万
@@ -99565,7 +99556,7 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="H57" s="24" t="inlineStr">
+      <c r="H57" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $687万
@@ -99588,20 +99579,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C58" s="25" t="inlineStr">
+      <c r="C58" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D58" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
@@ -99620,15 +99611,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G58" s="23" t="inlineStr">
+      <c r="G58" s="22" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $685万
 $19,735/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H58" s="24" t="inlineStr">
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H58" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $687万
@@ -99651,20 +99642,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C59" s="25" t="inlineStr">
+      <c r="C59" s="24" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D59" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
@@ -99683,15 +99674,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G59" s="24" t="inlineStr">
+      <c r="G59" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
 $580万
 $16,723/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="H59" s="24" t="inlineStr">
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="H59" s="23" t="inlineStr">
         <is>
           <t>G | 457呎 (2房)
 $701万

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,18 +124,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -215,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -280,13 +275,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6378,7 +6370,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6580,7 +6572,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6914,7 +6906,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -7046,34 +7038,34 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>8780000</v>
+        <v>7389000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>19686</v>
+        <v>16567</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>7463000</v>
+        <v>7389000</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>16733</v>
+        <v>16567</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -7248,7 +7240,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -7385,7 +7377,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7582,7 +7574,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7916,7 +7908,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -8250,7 +8242,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8584,7 +8576,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -8918,7 +8910,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -9252,7 +9244,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -9920,7 +9912,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -10254,7 +10246,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -10588,7 +10580,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10922,7 +10914,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -11256,34 +11248,34 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
-        <v>10241000</v>
+        <v>8909600</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>21697</v>
+        <v>18876</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="5" t="n">
-        <v>8704850</v>
+        <v>8909600</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>18442</v>
+        <v>18876</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N156" s="3" t="inlineStr">
@@ -12263,7 +12255,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -12584,7 +12576,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -12910,7 +12902,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -13567,7 +13559,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -14214,7 +14206,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -14540,7 +14532,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14871,7 +14863,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -15849,7 +15841,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -17800,7 +17792,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -18931,7 +18923,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -24238,7 +24230,7 @@
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -24650,7 +24642,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -25062,7 +25054,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -25474,7 +25466,7 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -25886,7 +25878,7 @@
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G373" s="3" t="inlineStr">
@@ -26228,7 +26220,7 @@
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -26290,7 +26282,7 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -26632,7 +26624,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -26694,7 +26686,7 @@
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -27036,7 +27028,7 @@
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
@@ -27098,7 +27090,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -27440,7 +27432,7 @@
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
@@ -27502,7 +27494,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -27844,7 +27836,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -27906,7 +27898,7 @@
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
@@ -28248,7 +28240,7 @@
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
@@ -28310,7 +28302,7 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -28652,7 +28644,7 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -28714,7 +28706,7 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -29056,7 +29048,7 @@
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -29118,7 +29110,7 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -29460,7 +29452,7 @@
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
@@ -29522,34 +29514,34 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
-        <v>10651000</v>
+        <v>9053000</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>19226</v>
+        <v>16341</v>
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K427" s="5" t="n">
-        <v>9053350</v>
+        <v>9053000</v>
       </c>
       <c r="L427" s="5" t="n">
-        <v>16342</v>
+        <v>16341</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N427" s="3" t="inlineStr">
@@ -29864,7 +29856,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -29926,7 +29918,7 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -30268,7 +30260,7 @@
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
@@ -30672,7 +30664,7 @@
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
@@ -31076,7 +31068,7 @@
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
@@ -31480,7 +31472,7 @@
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G456" s="3" t="inlineStr">
@@ -31884,7 +31876,7 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -32288,7 +32280,7 @@
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
@@ -32684,7 +32676,7 @@
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -33088,7 +33080,7 @@
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
@@ -33492,7 +33484,7 @@
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
@@ -33896,7 +33888,7 @@
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
@@ -34300,7 +34292,7 @@
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
@@ -34704,7 +34696,7 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -35517,7 +35509,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -35921,7 +35913,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -36325,7 +36317,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -37941,7 +37933,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -39961,7 +39953,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -40365,7 +40357,7 @@
       </c>
       <c r="G588" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H588" s="5" t="n">
@@ -41168,7 +41160,7 @@
       </c>
       <c r="F600" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G600" s="3" t="inlineStr">
@@ -41235,7 +41227,7 @@
       </c>
       <c r="G601" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H601" s="5" t="n">
@@ -41572,7 +41564,7 @@
       </c>
       <c r="F606" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G606" s="3" t="inlineStr">
@@ -47856,7 +47848,7 @@
       </c>
       <c r="F696" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G696" s="3" t="inlineStr">
@@ -47980,7 +47972,7 @@
       </c>
       <c r="F698" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G698" s="3" t="inlineStr">
@@ -48244,7 +48236,7 @@
       </c>
       <c r="F702" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G702" s="3" t="inlineStr">
@@ -48306,7 +48298,7 @@
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G703" s="3" t="inlineStr">
@@ -48508,7 +48500,7 @@
       </c>
       <c r="F706" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G706" s="3" t="inlineStr">
@@ -48570,7 +48562,7 @@
       </c>
       <c r="F707" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G707" s="3" t="inlineStr">
@@ -48632,7 +48624,7 @@
       </c>
       <c r="F708" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G708" s="3" t="inlineStr">
@@ -48834,7 +48826,7 @@
       </c>
       <c r="F711" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G711" s="3" t="inlineStr">
@@ -48896,7 +48888,7 @@
       </c>
       <c r="F712" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G712" s="3" t="inlineStr">
@@ -48958,7 +48950,7 @@
       </c>
       <c r="F713" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G713" s="3" t="inlineStr">
@@ -49160,7 +49152,7 @@
       </c>
       <c r="F716" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G716" s="3" t="inlineStr">
@@ -49222,7 +49214,7 @@
       </c>
       <c r="F717" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G717" s="3" t="inlineStr">
@@ -49284,7 +49276,7 @@
       </c>
       <c r="F718" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G718" s="3" t="inlineStr">
@@ -49548,7 +49540,7 @@
       </c>
       <c r="F722" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G722" s="3" t="inlineStr">
@@ -49610,7 +49602,7 @@
       </c>
       <c r="F723" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G723" s="3" t="inlineStr">
@@ -49874,7 +49866,7 @@
       </c>
       <c r="F727" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G727" s="3" t="inlineStr">
@@ -49936,7 +49928,7 @@
       </c>
       <c r="F728" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G728" s="3" t="inlineStr">
@@ -50200,7 +50192,7 @@
       </c>
       <c r="F732" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G732" s="3" t="inlineStr">
@@ -50262,7 +50254,7 @@
       </c>
       <c r="F733" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G733" s="3" t="inlineStr">
@@ -50526,7 +50518,7 @@
       </c>
       <c r="F737" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G737" s="3" t="inlineStr">
@@ -50588,7 +50580,7 @@
       </c>
       <c r="F738" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G738" s="3" t="inlineStr">
@@ -50852,7 +50844,7 @@
       </c>
       <c r="F742" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G742" s="3" t="inlineStr">
@@ -50914,34 +50906,34 @@
       </c>
       <c r="F743" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G743" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H743" s="5" t="n">
-        <v>9128000</v>
+        <v>7941300</v>
       </c>
       <c r="I743" s="5" t="n">
-        <v>18705</v>
+        <v>16273</v>
       </c>
       <c r="J743" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K743" s="5" t="n">
-        <v>7758800</v>
+        <v>7941300</v>
       </c>
       <c r="L743" s="5" t="n">
-        <v>15899</v>
+        <v>16273</v>
       </c>
       <c r="M743" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N743" s="3" t="inlineStr">
@@ -51178,7 +51170,7 @@
       </c>
       <c r="F747" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G747" s="3" t="inlineStr">
@@ -51892,23 +51884,23 @@
       </c>
       <c r="F758" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G758" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H758" s="5" t="n">
-        <v>9092000</v>
+        <v>7728200</v>
       </c>
       <c r="I758" s="5" t="n">
-        <v>18631</v>
+        <v>15836</v>
       </c>
       <c r="J758" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K758" s="5" t="n">
@@ -51919,7 +51911,7 @@
       </c>
       <c r="M758" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N758" s="3" t="inlineStr">
@@ -55529,7 +55521,7 @@
       </c>
       <c r="G814" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H814" s="5" t="n">
@@ -55847,7 +55839,7 @@
       </c>
       <c r="G819" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H819" s="5" t="n">
@@ -59239,7 +59231,7 @@
       </c>
       <c r="G871" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H871" s="5" t="n">
@@ -61308,7 +61300,7 @@
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G902" s="3" t="inlineStr">
@@ -61790,7 +61782,7 @@
       </c>
       <c r="F909" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G909" s="3" t="inlineStr">
@@ -62272,7 +62264,7 @@
       </c>
       <c r="F916" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G916" s="3" t="inlineStr">
@@ -62754,7 +62746,7 @@
       </c>
       <c r="F923" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G923" s="3" t="inlineStr">
@@ -63236,7 +63228,7 @@
       </c>
       <c r="F930" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G930" s="3" t="inlineStr">
@@ -63718,7 +63710,7 @@
       </c>
       <c r="F937" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G937" s="3" t="inlineStr">
@@ -64200,7 +64192,7 @@
       </c>
       <c r="F944" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G944" s="3" t="inlineStr">
@@ -64682,7 +64674,7 @@
       </c>
       <c r="F951" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G951" s="3" t="inlineStr">
@@ -65164,7 +65156,7 @@
       </c>
       <c r="F958" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G958" s="3" t="inlineStr">
@@ -65646,7 +65638,7 @@
       </c>
       <c r="F965" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G965" s="3" t="inlineStr">
@@ -66128,7 +66120,7 @@
       </c>
       <c r="F972" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G972" s="3" t="inlineStr">
@@ -66610,7 +66602,7 @@
       </c>
       <c r="F979" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G979" s="3" t="inlineStr">
@@ -67092,7 +67084,7 @@
       </c>
       <c r="F986" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G986" s="3" t="inlineStr">
@@ -67574,7 +67566,7 @@
       </c>
       <c r="F993" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G993" s="3" t="inlineStr">
@@ -68056,7 +68048,7 @@
       </c>
       <c r="F1000" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1000" s="3" t="inlineStr">
@@ -69564,7 +69556,7 @@
       </c>
       <c r="F1022" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1022" s="3" t="inlineStr">
@@ -70038,7 +70030,7 @@
       </c>
       <c r="F1029" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1029" s="3" t="inlineStr">
@@ -70504,7 +70496,7 @@
       </c>
       <c r="F1036" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1036" s="3" t="inlineStr">
@@ -70978,7 +70970,7 @@
       </c>
       <c r="F1043" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1043" s="3" t="inlineStr">
@@ -71452,7 +71444,7 @@
       </c>
       <c r="F1050" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1050" s="3" t="inlineStr">
@@ -71926,7 +71918,7 @@
       </c>
       <c r="F1057" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1057" s="3" t="inlineStr">
@@ -72400,7 +72392,7 @@
       </c>
       <c r="F1064" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1064" s="3" t="inlineStr">
@@ -72874,7 +72866,7 @@
       </c>
       <c r="F1071" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1071" s="3" t="inlineStr">
@@ -73348,7 +73340,7 @@
       </c>
       <c r="F1078" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1078" s="3" t="inlineStr">
@@ -73822,7 +73814,7 @@
       </c>
       <c r="F1085" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1085" s="3" t="inlineStr">
@@ -74288,7 +74280,7 @@
       </c>
       <c r="F1092" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1092" s="3" t="inlineStr">
@@ -74746,7 +74738,7 @@
       </c>
       <c r="F1099" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1099" s="3" t="inlineStr">
@@ -75018,38 +75010,30 @@
       </c>
       <c r="F1103" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1103" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1103" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H1103" s="5" t="n">
+        <v>15490000</v>
+      </c>
+      <c r="I1103" s="5" t="n">
+        <v>19783</v>
       </c>
       <c r="J1103" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1103" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1103" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1103" s="5" t="n">
+        <v>15490000</v>
+      </c>
+      <c r="L1103" s="5" t="n">
+        <v>19783</v>
       </c>
       <c r="M1103" s="3" t="inlineStr">
         <is>
@@ -75058,7 +75042,7 @@
       </c>
       <c r="N1103" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -75220,7 +75204,7 @@
       </c>
       <c r="F1106" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1106" s="3" t="inlineStr">
@@ -75686,7 +75670,7 @@
       </c>
       <c r="F1113" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1113" s="3" t="inlineStr">
@@ -76152,7 +76136,7 @@
       </c>
       <c r="F1120" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1120" s="3" t="inlineStr">
@@ -76610,7 +76594,7 @@
       </c>
       <c r="F1127" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1127" s="3" t="inlineStr">
@@ -77076,7 +77060,7 @@
       </c>
       <c r="F1134" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1134" s="3" t="inlineStr">
@@ -77542,7 +77526,7 @@
       </c>
       <c r="F1141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1141" s="3" t="inlineStr">
@@ -78008,7 +77992,7 @@
       </c>
       <c r="F1148" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1148" s="3" t="inlineStr">
@@ -78479,7 +78463,7 @@
       </c>
       <c r="G1155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H1155" s="5" t="n">
@@ -79872,7 +79856,7 @@
       </c>
       <c r="F1176" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1176" s="3" t="inlineStr">
@@ -86026,7 +86010,7 @@
       </c>
       <c r="F1267" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1267" s="3" t="inlineStr">
@@ -87449,17 +87433,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88261,7 +88245,7 @@
           <t>A | 472呎 (2房)
 $1053万
 $22,314/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -88285,7 +88269,7 @@
           <t>D | 446呎 (2房)
 $881万
 $19,747/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -88308,7 +88292,7 @@
           <t>A | 472呎 (2房)
 $1051万
 $22,269/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -88355,7 +88339,7 @@
           <t>A | 472呎 (2房)
 $1049万
 $22,222/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -88374,12 +88358,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$878万
-$19,686/呎
-(已定价未售)</t>
+$739万
+$16,567/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -88402,7 +88386,7 @@
           <t>A | 472呎 (2房)
 $1049万
 $22,222/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -88426,7 +88410,7 @@
           <t>D | 446呎 (2房)
 $739万
 $16,567/呎
-(26年-09月-06日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -88449,7 +88433,7 @@
           <t>A | 472呎 (2房)
 $1045万
 $22,136/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -88496,7 +88480,7 @@
           <t>A | 472呎 (2房)
 $1043万
 $22,091/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -88543,7 +88527,7 @@
           <t>A | 472呎 (2房)
 $1041万
 $22,047/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -88590,7 +88574,7 @@
           <t>A | 472呎 (2房)
 $1039万
 $22,004/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -88637,7 +88621,7 @@
           <t>A | 472呎 (2房)
 $1036万
 $21,960/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -88731,7 +88715,7 @@
           <t>A | 472呎 (2房)
 $1032万
 $21,873/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -88778,7 +88762,7 @@
           <t>A | 472呎 (2房)
 $1030万
 $21,826/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -88825,7 +88809,7 @@
           <t>A | 472呎 (2房)
 $1030万
 $21,826/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -88872,7 +88856,7 @@
           <t>A | 472呎 (2房)
 $1026万
 $21,742/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -88914,12 +88898,12 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1024万
-$21,697/呎
-(已定价未售)</t>
+$891万
+$18,876/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -89060,7 +89044,7 @@
           <t>A | 472呎 (2房)
 $865万
 $18,333/呎
-(26年-08月-28日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -89107,7 +89091,7 @@
           <t>A | 472呎 (2房)
 $1021万
 $21,633/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -89154,7 +89138,7 @@
           <t>A | 472呎 (2房)
 $1019万
 $21,591/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
@@ -89248,7 +89232,7 @@
           <t>A | 472呎 (2房)
 $880万
 $18,651/呎
-(26年-08月-28日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
@@ -89342,7 +89326,7 @@
           <t>A | 472呎 (2房)
 $1011万
 $21,417/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
@@ -89389,7 +89373,7 @@
           <t>A | 472呎 (2房)
 $1009万
 $21,375/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -89436,7 +89420,7 @@
           <t>A | 472呎 (2房)
 $850万
 $18,007/呎
-(26年-08月-28日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
@@ -89577,7 +89561,7 @@
           <t>A | 472呎 (2房)
 $845万
 $17,899/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
@@ -89859,7 +89843,7 @@
           <t>A | 472呎 (2房)
 $992万
 $21,015/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -90071,7 +90055,7 @@
           <t>D | 446呎 (2房)
 $699万
 $15,675/呎
-(26年-08月-30日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
@@ -90204,17 +90188,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -90898,7 +90882,7 @@
           <t>D | 555呎 (2房)
 $1106万
 $19,926/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -90953,7 +90937,7 @@
           <t>D | 555呎 (2房)
 $1104万
 $19,895/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -91008,7 +90992,7 @@
           <t>D | 555呎 (2房)
 $1103万
 $19,867/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -91063,7 +91047,7 @@
           <t>D | 555呎 (2房)
 $1101万
 $19,836/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -91118,7 +91102,7 @@
           <t>D | 555呎 (2房)
 $1099万
 $19,805/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -91152,7 +91136,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91173,7 +91157,7 @@
           <t>D | 554呎 (2房)
 $1078万
 $19,458/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -91181,7 +91165,7 @@
           <t>E | 453呎 (2房)
 $912万
 $20,121/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -91207,7 +91191,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91228,7 +91212,7 @@
           <t>D | 554呎 (2房)
 $1076万
 $19,430/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -91236,7 +91220,7 @@
           <t>E | 453呎 (2房)
 $910万
 $20,084/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -91262,7 +91246,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91283,7 +91267,7 @@
           <t>D | 554呎 (2房)
 $1075万
 $19,399/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -91291,7 +91275,7 @@
           <t>E | 453呎 (2房)
 $908万
 $20,042/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -91317,7 +91301,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91338,7 +91322,7 @@
           <t>D | 554呎 (2房)
 $1075万
 $19,399/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -91346,7 +91330,7 @@
           <t>E | 453呎 (2房)
 $908万
 $20,042/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -91372,7 +91356,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91393,7 +91377,7 @@
           <t>D | 554呎 (2房)
 $1072万
 $19,341/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -91401,7 +91385,7 @@
           <t>E | 453呎 (2房)
 $904万
 $19,960/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -91427,7 +91411,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91448,7 +91432,7 @@
           <t>D | 554呎 (2房)
 $1070万
 $19,312/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -91456,7 +91440,7 @@
           <t>E | 453呎 (2房)
 $902万
 $19,923/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -91482,7 +91466,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91503,7 +91487,7 @@
           <t>D | 554呎 (2房)
 $1068万
 $19,285/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -91511,7 +91495,7 @@
           <t>E | 453呎 (2房)
 $901万
 $19,883/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -91537,7 +91521,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91558,7 +91542,7 @@
           <t>D | 554呎 (2房)
 $1067万
 $19,255/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -91566,7 +91550,7 @@
           <t>E | 453呎 (2房)
 $899万
 $19,843/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -91592,7 +91576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91608,12 +91592,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1065万
-$19,226/呎
-(已定价未售)</t>
+$905万
+$16,341/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -91621,7 +91605,7 @@
           <t>E | 453呎 (2房)
 $897万
 $19,804/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -91647,7 +91631,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91668,7 +91652,7 @@
           <t>D | 554呎 (2房)
 $1064万
 $19,197/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -91676,7 +91660,7 @@
           <t>E | 453呎 (2房)
 $895万
 $19,764/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -91702,7 +91686,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91731,7 +91715,7 @@
           <t>E | 453呎 (2房)
 $894万
 $19,724/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -91757,7 +91741,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91786,7 +91770,7 @@
           <t>E | 453呎 (2房)
 $892万
 $19,687/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -91812,7 +91796,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91841,7 +91825,7 @@
           <t>E | 453呎 (2房)
 $892万
 $19,687/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -91867,7 +91851,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91896,7 +91880,7 @@
           <t>E | 453呎 (2房)
 $888万
 $19,605/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -91922,7 +91906,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -91951,7 +91935,7 @@
           <t>E | 453呎 (2房)
 $886万
 $19,567/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -92006,7 +91990,7 @@
           <t>E | 453呎 (2房)
 $885万
 $19,528/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -92032,7 +92016,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92061,7 +92045,7 @@
           <t>E | 453呎 (2房)
 $883万
 $19,488/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
@@ -92087,7 +92071,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92116,7 +92100,7 @@
           <t>E | 453呎 (2房)
 $881万
 $19,450/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -92142,7 +92126,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92171,7 +92155,7 @@
           <t>E | 453呎 (2房)
 $879万
 $19,411/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
@@ -92197,7 +92181,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92226,7 +92210,7 @@
           <t>E | 453呎 (2房)
 $878万
 $19,373/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
@@ -92252,7 +92236,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92281,7 +92265,7 @@
           <t>E | 453呎 (2房)
 $876万
 $19,336/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr">
@@ -92307,7 +92291,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92336,7 +92320,7 @@
           <t>E | 453呎 (2房)
 $876万
 $19,336/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
@@ -92362,7 +92346,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92417,7 +92401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92446,7 +92430,7 @@
           <t>E | 453呎 (2房)
 $757万
 $16,720/呎
-(26年-08月-28日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="G44" s="20" t="inlineStr">
@@ -92472,7 +92456,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C45" s="22" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
 招标单位
@@ -92501,7 +92485,7 @@
           <t>E | 453呎 (2房)
 $756万
 $16,685/呎
-(26年-08月-28日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
@@ -92556,7 +92540,7 @@
           <t>E | 453呎 (2房)
 $753万
 $16,620/呎
-(26年-08月-28日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="G46" s="20" t="inlineStr">
@@ -92776,7 +92760,7 @@
           <t>E | 453呎 (2房)
 $748万
 $16,520/呎
-(26年-08月-28日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G50" s="20" t="inlineStr">
@@ -93051,7 +93035,7 @@
           <t>E | 453呎 (2房)
 $740万
 $16,325/呎
-(26年-08月-28日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G55" s="20" t="inlineStr">
@@ -93106,7 +93090,7 @@
           <t>E | 453呎 (2房)
 $721万
 $15,915/呎
-(26年-08月-28日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="G56" s="20" t="inlineStr">
@@ -93208,7 +93192,7 @@
           <t>D | 554呎 (2房)
 $887万
 $16,015/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
@@ -93216,7 +93200,7 @@
           <t>E | 453呎 (2房)
 $855万
 $18,876/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G58" s="20" t="inlineStr">
@@ -93271,7 +93255,7 @@
           <t>E | 453呎 (2房)
 $852万
 $18,799/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G59" s="20" t="inlineStr">
@@ -93411,17 +93395,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -93521,7 +93505,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93568,7 +93552,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93615,7 +93599,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93662,7 +93646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93709,7 +93693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93756,7 +93740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93803,7 +93787,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93850,7 +93834,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93897,7 +93881,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93944,7 +93928,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -93991,7 +93975,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94038,7 +94022,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94085,7 +94069,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94132,7 +94116,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94179,7 +94163,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94226,7 +94210,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94239,7 +94223,7 @@
           <t>C | 488呎 (2房)
 $929万
 $19,045/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -94255,7 +94239,7 @@
           <t>E | 464呎 (2房)
 $885万
 $19,065/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94273,7 +94257,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94286,7 +94270,7 @@
           <t>C | 488呎 (2房)
 $928万
 $19,006/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -94294,7 +94278,7 @@
           <t>D | 445呎 (2房)
 $869万
 $19,521/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -94320,7 +94304,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94333,7 +94317,7 @@
           <t>C | 488呎 (2房)
 $926万
 $18,967/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -94341,7 +94325,7 @@
           <t>D | 445呎 (2房)
 $867万
 $19,492/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -94349,7 +94333,7 @@
           <t>E | 464呎 (2房)
 $882万
 $19,009/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94367,7 +94351,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94380,7 +94364,7 @@
           <t>C | 488呎 (2房)
 $926万
 $18,967/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -94388,7 +94372,7 @@
           <t>D | 445呎 (2房)
 $867万
 $19,492/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -94396,7 +94380,7 @@
           <t>E | 464呎 (2房)
 $882万
 $19,009/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94414,7 +94398,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94427,7 +94411,7 @@
           <t>C | 488呎 (2房)
 $922万
 $18,893/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -94435,7 +94419,7 @@
           <t>D | 445呎 (2房)
 $865万
 $19,434/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -94443,7 +94427,7 @@
           <t>E | 464呎 (2房)
 $879万
 $18,950/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -94461,7 +94445,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94474,7 +94458,7 @@
           <t>C | 488呎 (2房)
 $920万
 $18,855/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -94482,7 +94466,7 @@
           <t>D | 445呎 (2房)
 $864万
 $19,404/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -94508,7 +94492,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94521,7 +94505,7 @@
           <t>C | 488呎 (2房)
 $918万
 $18,820/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -94529,7 +94513,7 @@
           <t>D | 445呎 (2房)
 $862万
 $19,375/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -94555,7 +94539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94568,7 +94552,7 @@
           <t>C | 488呎 (2房)
 $916万
 $18,781/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -94576,7 +94560,7 @@
           <t>D | 445呎 (2房)
 $861万
 $19,346/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -94602,7 +94586,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94615,7 +94599,7 @@
           <t>C | 488呎 (2房)
 $915万
 $18,742/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -94623,7 +94607,7 @@
           <t>D | 445呎 (2房)
 $860万
 $19,317/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
@@ -94649,7 +94633,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94657,12 +94641,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$913万
-$18,705/呎
-(已定价未售)</t>
+$794万
+$16,273/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -94670,7 +94654,7 @@
           <t>D | 445呎 (2房)
 $858万
 $19,290/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -94696,7 +94680,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94717,7 +94701,7 @@
           <t>D | 445呎 (2房)
 $857万
 $19,261/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -94743,7 +94727,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94790,7 +94774,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94798,12 +94782,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$909万
-$18,631/呎
-(在售)</t>
+$773万
+$15,836/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -94837,7 +94821,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94884,7 +94868,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94931,7 +94915,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -94978,7 +94962,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95025,7 +95009,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95166,7 +95150,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95213,7 +95197,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95260,7 +95244,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95312,7 +95296,7 @@
           <t>B | 602呎 (2房)
 $1090万
 $18,115/呎
-(26年-08月-31日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
@@ -95359,7 +95343,7 @@
           <t>B | 602呎 (2房)
 $1116万
 $18,530/呎
-(26年-08月-26日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
@@ -95401,7 +95385,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
 招标单位
@@ -95900,7 +95884,7 @@
           <t>E | 464呎 (2房)
 $712万
 $15,353/呎
-(26年-08月-27日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -96167,17 +96151,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -96303,7 +96287,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96311,7 +96295,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96348,7 +96332,7 @@
           <t>G | 459呎 (2房)
 $908万
 $19,782/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96366,7 +96350,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96374,7 +96358,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96411,7 +96395,7 @@
           <t>G | 459呎 (2房)
 $906万
 $19,743/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96429,7 +96413,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96437,7 +96421,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96474,7 +96458,7 @@
           <t>G | 459呎 (2房)
 $904万
 $19,704/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96492,7 +96476,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96500,7 +96484,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96537,7 +96521,7 @@
           <t>G | 459呎 (2房)
 $904万
 $19,704/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96555,7 +96539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96563,7 +96547,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96600,7 +96584,7 @@
           <t>G | 459呎 (2房)
 $901万
 $19,625/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96618,7 +96602,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96626,7 +96610,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96663,7 +96647,7 @@
           <t>G | 459呎 (2房)
 $899万
 $19,584/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96681,7 +96665,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96689,7 +96673,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96726,7 +96710,7 @@
           <t>G | 459呎 (2房)
 $897万
 $19,547/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96744,7 +96728,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96752,7 +96736,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96789,7 +96773,7 @@
           <t>G | 459呎 (2房)
 $895万
 $19,508/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96807,7 +96791,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96815,7 +96799,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96852,7 +96836,7 @@
           <t>G | 459呎 (2房)
 $894万
 $19,468/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96870,7 +96854,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96878,7 +96862,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96915,7 +96899,7 @@
           <t>G | 459呎 (2房)
 $892万
 $19,431/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96933,7 +96917,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -96941,7 +96925,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -96978,7 +96962,7 @@
           <t>G | 459呎 (2房)
 $890万
 $19,390/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -96996,7 +96980,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97004,7 +96988,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97041,7 +97025,7 @@
           <t>G | 459呎 (2房)
 $888万
 $19,351/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97059,7 +97043,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97067,7 +97051,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97104,7 +97088,7 @@
           <t>G | 459呎 (2房)
 $886万
 $19,314/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97122,7 +97106,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97130,7 +97114,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97167,7 +97151,7 @@
           <t>G | 459呎 (2房)
 $885万
 $19,275/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97185,7 +97169,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97193,7 +97177,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 595呎 (2房)
 招标单位
@@ -97230,7 +97214,7 @@
           <t>G | 459呎 (2房)
 $883万
 $19,235/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -97248,7 +97232,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97256,7 +97240,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97311,7 +97295,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97319,7 +97303,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97374,7 +97358,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97382,7 +97366,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97411,7 +97395,7 @@
           <t>F | 347呎 (1房)
 $722万
 $20,795/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -97445,7 +97429,7 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97474,7 +97458,7 @@
           <t>F | 347呎 (1房)
 $722万
 $20,795/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -97500,7 +97484,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97508,7 +97492,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97537,7 +97521,7 @@
           <t>F | 347呎 (1房)
 $720万
 $20,735/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -97563,7 +97547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97571,7 +97555,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97600,7 +97584,7 @@
           <t>F | 347呎 (1房)
 $718万
 $20,706/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -97626,7 +97610,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97634,7 +97618,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97663,7 +97647,7 @@
           <t>F | 347呎 (1房)
 $717万
 $20,674/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
@@ -97689,7 +97673,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97697,7 +97681,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97726,7 +97710,7 @@
           <t>F | 347呎 (1房)
 $716万
 $20,646/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -97752,7 +97736,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97760,7 +97744,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97789,7 +97773,7 @@
           <t>F | 347呎 (1房)
 $715万
 $20,611/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
@@ -97815,7 +97799,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97823,7 +97807,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97852,7 +97836,7 @@
           <t>F | 347呎 (1房)
 $714万
 $20,579/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -97878,7 +97862,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -97886,7 +97870,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97915,7 +97899,7 @@
           <t>F | 347呎 (1房)
 $713万
 $20,550/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -97949,7 +97933,7 @@
 (26年-09月-04日)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -97978,7 +97962,7 @@
           <t>F | 347呎 (1房)
 $712万
 $20,519/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
@@ -98041,7 +98025,7 @@
           <t>F | 347呎 (1房)
 $712万
 $20,519/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
@@ -98067,15 +98051,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
+$1549万
+$19,783/呎
+(26年-09月-18日)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98104,7 +98088,7 @@
           <t>F | 347呎 (1房)
 $710万
 $20,458/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
@@ -98138,7 +98122,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98167,7 +98151,7 @@
           <t>F | 347呎 (1房)
 $709万
 $20,427/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
@@ -98201,7 +98185,7 @@
 (26年-09月-17日)</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98230,7 +98214,7 @@
           <t>F | 347呎 (1房)
 $708万
 $20,398/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr">
@@ -98293,7 +98277,7 @@
           <t>F | 347呎 (1房)
 $707万
 $20,366/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
@@ -98327,7 +98311,7 @@
 (26年-08月-07日)</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98356,7 +98340,7 @@
           <t>F | 347呎 (1房)
 $706万
 $20,334/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
@@ -98390,7 +98374,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98419,7 +98403,7 @@
           <t>F | 347呎 (1房)
 $705万
 $20,305/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H39" s="23" t="inlineStr">
@@ -98453,7 +98437,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98482,7 +98466,7 @@
           <t>F | 347呎 (1房)
 $704万
 $20,274/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H40" s="23" t="inlineStr">
@@ -98516,7 +98500,7 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98545,7 +98529,7 @@
           <t>F | 347呎 (1房)
 $702万
 $20,245/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H41" s="23" t="inlineStr">
@@ -98579,7 +98563,7 @@
 (26年-09月-07日)</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D42" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98608,7 +98592,7 @@
           <t>F | 347呎 (1房)
 $597万
 $17,208/呎
-(26年-09月-02日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="H42" s="23" t="inlineStr">
@@ -98642,7 +98626,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D43" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98705,7 +98689,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D44" s="24" t="inlineStr">
+      <c r="D44" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98768,7 +98752,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="D45" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98797,7 +98781,7 @@
           <t>F | 347呎 (1房)
 $698万
 $20,121/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H45" s="23" t="inlineStr">
@@ -98823,7 +98807,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98831,7 +98815,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D46" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98886,7 +98870,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C47" s="24" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98894,7 +98878,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="D47" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -98949,7 +98933,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C48" s="24" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -98957,7 +98941,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D48" s="24" t="inlineStr">
+      <c r="D48" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99012,7 +98996,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99020,7 +99004,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D49" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99075,7 +99059,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99083,7 +99067,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D50" s="24" t="inlineStr">
+      <c r="D50" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99138,7 +99122,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99146,7 +99130,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="D51" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99201,7 +99185,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99209,7 +99193,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D52" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99264,7 +99248,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99272,7 +99256,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D53" s="24" t="inlineStr">
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99327,7 +99311,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99335,7 +99319,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D54" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99390,7 +99374,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C55" s="24" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99398,7 +99382,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="D55" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99453,7 +99437,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99461,7 +99445,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99516,7 +99500,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99524,7 +99508,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="D57" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99579,7 +99563,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C58" s="24" t="inlineStr">
+      <c r="C58" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99587,7 +99571,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D58" s="24" t="inlineStr">
+      <c r="D58" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -99616,7 +99600,7 @@
           <t>F | 347呎 (1房)
 $685万
 $19,735/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H58" s="23" t="inlineStr">
@@ -99642,7 +99626,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C59" s="24" t="inlineStr">
+      <c r="C59" s="22" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
 招标单位
@@ -99650,7 +99634,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="D59" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="H86" s="5" t="n">
-        <v>10532000</v>
+        <v>10585000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>22314</v>
+        <v>22426</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="K86" s="5" t="n">
-        <v>8952200</v>
+        <v>8997250</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>18967</v>
+        <v>19062</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>10511000</v>
+        <v>10564000</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>22269</v>
+        <v>22381</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>8934350</v>
+        <v>8979400</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>18929</v>
+        <v>19024</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -14206,34 +14206,34 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>10109000</v>
+        <v>8592600</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>21417</v>
+        <v>18205</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K201" s="5" t="n">
-        <v>8592650</v>
+        <v>8592600</v>
       </c>
       <c r="L201" s="5" t="n">
         <v>18205</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -17792,34 +17792,34 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
-        <v>9919000</v>
+        <v>8347800</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>21015</v>
+        <v>17686</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K256" s="5" t="n">
-        <v>8431150</v>
+        <v>8347800</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>17863</v>
+        <v>17686</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -26291,10 +26291,10 @@
         </is>
       </c>
       <c r="H379" s="5" t="n">
-        <v>10780000</v>
+        <v>10833000</v>
       </c>
       <c r="I379" s="5" t="n">
-        <v>19458</v>
+        <v>19554</v>
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
@@ -26302,10 +26302,10 @@
         </is>
       </c>
       <c r="K379" s="5" t="n">
-        <v>9163000</v>
+        <v>9208050</v>
       </c>
       <c r="L379" s="5" t="n">
-        <v>16540</v>
+        <v>16621</v>
       </c>
       <c r="M379" s="3" t="inlineStr">
         <is>
@@ -26695,10 +26695,10 @@
         </is>
       </c>
       <c r="H385" s="5" t="n">
-        <v>10764000</v>
+        <v>10818000</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>19430</v>
+        <v>19527</v>
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
@@ -26706,10 +26706,10 @@
         </is>
       </c>
       <c r="K385" s="5" t="n">
-        <v>9149400</v>
+        <v>9195300</v>
       </c>
       <c r="L385" s="5" t="n">
-        <v>16515</v>
+        <v>16598</v>
       </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
@@ -28302,34 +28302,34 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
-        <v>10699000</v>
+        <v>9094100</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>19312</v>
+        <v>16415</v>
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>9094150</v>
+        <v>9094100</v>
       </c>
       <c r="L409" s="5" t="n">
         <v>16415</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N409" s="3" t="inlineStr">
@@ -29918,34 +29918,34 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
-        <v>10635000</v>
+        <v>9039700</v>
       </c>
       <c r="I433" s="5" t="n">
-        <v>19197</v>
+        <v>16317</v>
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K433" s="5" t="n">
-        <v>9039750</v>
+        <v>9039700</v>
       </c>
       <c r="L433" s="5" t="n">
         <v>16317</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N433" s="3" t="inlineStr">
@@ -32870,38 +32870,30 @@
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H477" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I477" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H477" s="5" t="n">
+        <v>12520000</v>
+      </c>
+      <c r="I477" s="5" t="n">
+        <v>19936</v>
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K477" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L477" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K477" s="5" t="n">
+        <v>12520000</v>
+      </c>
+      <c r="L477" s="5" t="n">
+        <v>19936</v>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
@@ -32910,7 +32902,7 @@
       </c>
       <c r="N477" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33484,34 +33476,34 @@
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
-        <v>8793000</v>
+        <v>7474000</v>
       </c>
       <c r="I486" s="5" t="n">
-        <v>19411</v>
+        <v>16499</v>
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K486" s="5" t="n">
-        <v>7474050</v>
+        <v>7474000</v>
       </c>
       <c r="L486" s="5" t="n">
         <v>16499</v>
       </c>
       <c r="M486" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N486" s="3" t="inlineStr">
@@ -33888,23 +33880,23 @@
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
-        <v>8776000</v>
+        <v>7459600</v>
       </c>
       <c r="I492" s="5" t="n">
-        <v>19373</v>
+        <v>16467</v>
       </c>
       <c r="J492" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K492" s="5" t="n">
@@ -33915,7 +33907,7 @@
       </c>
       <c r="M492" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N492" s="3" t="inlineStr">
@@ -36721,7 +36713,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -37529,7 +37521,7 @@
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
@@ -38337,7 +38329,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -39145,7 +39137,7 @@
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H570" s="5" t="n">
@@ -39549,7 +39541,7 @@
       </c>
       <c r="G576" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H576" s="5" t="n">
@@ -49152,34 +49144,34 @@
       </c>
       <c r="F716" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G716" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H716" s="5" t="n">
-        <v>8793000</v>
+        <v>7474000</v>
       </c>
       <c r="I716" s="5" t="n">
-        <v>18950</v>
+        <v>16108</v>
       </c>
       <c r="J716" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K716" s="5" t="n">
-        <v>7474050</v>
+        <v>7474000</v>
       </c>
       <c r="L716" s="5" t="n">
         <v>16108</v>
       </c>
       <c r="M716" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N716" s="3" t="inlineStr">
@@ -50580,23 +50572,23 @@
       </c>
       <c r="F738" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G738" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H738" s="5" t="n">
-        <v>9146000</v>
+        <v>7774100</v>
       </c>
       <c r="I738" s="5" t="n">
-        <v>18742</v>
+        <v>15931</v>
       </c>
       <c r="J738" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K738" s="5" t="n">
@@ -50607,7 +50599,7 @@
       </c>
       <c r="M738" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N738" s="3" t="inlineStr">
@@ -51237,7 +51229,7 @@
       </c>
       <c r="G748" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H748" s="5" t="n">
@@ -52215,7 +52207,7 @@
       </c>
       <c r="G763" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H763" s="5" t="n">
@@ -52479,7 +52471,7 @@
       </c>
       <c r="G767" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H767" s="5" t="n">
@@ -52541,7 +52533,7 @@
       </c>
       <c r="G768" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H768" s="5" t="n">
@@ -60209,7 +60201,7 @@
       </c>
       <c r="G886" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H886" s="5" t="n">
@@ -60271,7 +60263,7 @@
       </c>
       <c r="G887" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H887" s="5" t="n">
@@ -61309,10 +61301,10 @@
         </is>
       </c>
       <c r="H902" s="5" t="n">
-        <v>9080000</v>
+        <v>9139000</v>
       </c>
       <c r="I902" s="5" t="n">
-        <v>19782</v>
+        <v>19911</v>
       </c>
       <c r="J902" s="3" t="inlineStr">
         <is>
@@ -61320,10 +61312,10 @@
         </is>
       </c>
       <c r="K902" s="5" t="n">
-        <v>7718000</v>
+        <v>7768150</v>
       </c>
       <c r="L902" s="5" t="n">
-        <v>16815</v>
+        <v>16924</v>
       </c>
       <c r="M902" s="3" t="inlineStr">
         <is>
@@ -61791,10 +61783,10 @@
         </is>
       </c>
       <c r="H909" s="5" t="n">
-        <v>9062000</v>
+        <v>9121000</v>
       </c>
       <c r="I909" s="5" t="n">
-        <v>19743</v>
+        <v>19871</v>
       </c>
       <c r="J909" s="3" t="inlineStr">
         <is>
@@ -61802,10 +61794,10 @@
         </is>
       </c>
       <c r="K909" s="5" t="n">
-        <v>7702700</v>
+        <v>7752850</v>
       </c>
       <c r="L909" s="5" t="n">
-        <v>16781</v>
+        <v>16891</v>
       </c>
       <c r="M909" s="3" t="inlineStr">
         <is>
@@ -74091,7 +74083,7 @@
       </c>
       <c r="G1089" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H1089" s="5" t="n">
@@ -77992,34 +77984,34 @@
       </c>
       <c r="F1148" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H1148" s="5" t="n">
-        <v>7025000</v>
+        <v>6111700</v>
       </c>
       <c r="I1148" s="5" t="n">
-        <v>20245</v>
+        <v>17613</v>
       </c>
       <c r="J1148" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1148" s="5" t="n">
-        <v>5971250</v>
+        <v>6111700</v>
       </c>
       <c r="L1148" s="5" t="n">
-        <v>17208</v>
+        <v>17613</v>
       </c>
       <c r="M1148" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1148" s="3" t="inlineStr">
@@ -81749,7 +81741,7 @@
       </c>
       <c r="G1204" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H1204" s="5" t="n">
@@ -87433,7 +87425,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87443,7 +87435,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88243,8 +88235,8 @@
       <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1053万
-$22,314/呎
+$1058万
+$22,426/呎
 (在售)</t>
         </is>
       </c>
@@ -88290,8 +88282,8 @@
       <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1051万
-$22,269/呎
+$1056万
+$22,381/呎
 (在售)</t>
         </is>
       </c>
@@ -88950,7 +88942,7 @@
           <t>A | 472呎 (2房)
 $889万
 $18,839/呎
-(26年-08月-28日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -89264,7 +89256,7 @@
           <t>E | 460呎 (2房)
 $770万
 $16,742/呎
-(26年-08月-28日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -89311,7 +89303,7 @@
           <t>E | 460呎 (2房)
 $767万
 $16,674/呎
-(26年-08月-28日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -89321,12 +89313,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B44" s="22" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1011万
-$21,417/呎
-(在售)</t>
+$859万
+$18,205/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
@@ -89514,7 +89506,7 @@
           <t>A | 472呎 (2房)
 $847万
 $17,935/呎
-(26年-08月-31日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
@@ -89838,12 +89830,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$992万
-$21,015/呎
-(在售)</t>
+$835万
+$17,686/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -90063,7 +90055,7 @@
           <t>E | 460呎 (2房)
 $724万
 $15,745/呎
-(26年-09月-06日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -90188,7 +90180,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90198,7 +90190,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -91155,8 +91147,8 @@
       <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1078万
-$19,458/呎
+$1083万
+$19,554/呎
 (在售)</t>
         </is>
       </c>
@@ -91210,8 +91202,8 @@
       <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1076万
-$19,430/呎
+$1082万
+$19,527/呎
 (在售)</t>
         </is>
       </c>
@@ -91427,12 +91419,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1070万
-$19,312/呎
-(在售)</t>
+$909万
+$16,415/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -91647,12 +91639,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1064万
-$19,197/呎
-(在售)</t>
+$904万
+$16,317/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -92016,12 +92008,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-招标单位
--
-(在售)</t>
+$1252万
+$19,936/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -92150,12 +92142,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$879万
-$19,411/呎
-(在售)</t>
+$747万
+$16,499/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
@@ -92205,12 +92197,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$878万
-$19,373/呎
-(在售)</t>
+$746万
+$16,467/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
@@ -92595,7 +92587,7 @@
           <t>E | 453呎 (2房)
 $751万
 $16,586/呎
-(26年-08月-28日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="G47" s="20" t="inlineStr">
@@ -92705,7 +92697,7 @@
           <t>E | 453呎 (2房)
 $748万
 $16,520/呎
-(26年-08月-28日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="G49" s="20" t="inlineStr">
@@ -92815,7 +92807,7 @@
           <t>E | 453呎 (2房)
 $745万
 $16,455/呎
-(26年-08月-28日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="G51" s="20" t="inlineStr">
@@ -92925,7 +92917,7 @@
           <t>E | 453呎 (2房)
 $742万
 $16,390/呎
-(26年-08月-28日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
@@ -92980,7 +92972,7 @@
           <t>E | 453呎 (2房)
 $741万
 $16,355/呎
-(26年-08月-28日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="G54" s="20" t="inlineStr">
@@ -93395,7 +93387,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93405,7 +93397,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94422,12 +94414,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
-$879万
-$18,950/呎
-(在售)</t>
+$747万
+$16,108/呎
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -94594,12 +94586,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$915万
-$18,742/呎
-(在售)</t>
+$777万
+$15,931/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -94693,7 +94685,7 @@
           <t>C | 488呎 (2房)
 $774万
 $15,866/呎
-(26年-08月-28日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -94834,7 +94826,7 @@
           <t>C | 488呎 (2房)
 $788万
 $16,143/呎
-(26年-08月-31日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -94881,7 +94873,7 @@
           <t>C | 488呎 (2房)
 $768万
 $15,742/呎
-(26年-08月-28日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -94889,7 +94881,7 @@
           <t>D | 445呎 (2房)
 $724万
 $16,272/呎
-(26年-08月-30日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
@@ -96017,7 +96009,7 @@
           <t>D | 445呎 (2房)
 $714万
 $16,043/呎
-(26年-09月-01日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
@@ -96025,7 +96017,7 @@
           <t>E | 464呎 (2房)
 $726万
 $15,645/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -96151,7 +96143,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96161,7 +96153,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -96330,8 +96322,8 @@
       <c r="H6" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
-$908万
-$19,782/呎
+$914万
+$19,911/呎
 (在售)</t>
         </is>
       </c>
@@ -96393,8 +96385,8 @@
       <c r="H7" s="22" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
-$906万
-$19,743/呎
+$912万
+$19,871/呎
 (在售)</t>
         </is>
       </c>
@@ -97930,7 +97922,7 @@
           <t>B | 783呎 (3房)
 $1510万
 $19,281/呎
-(26年-09月-04日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -98524,12 +98516,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="G41" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$702万
-$20,245/呎
-(在售)</t>
+$611万
+$17,613/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="H41" s="23" t="inlineStr">
@@ -99033,7 +99025,7 @@
           <t>F | 347呎 (1房)
 $589万
 $16,978/呎
-(26年-08月-29日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="H49" s="23" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -6370,34 +6370,34 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>8807000</v>
+        <v>7485900</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>19747</v>
+        <v>16785</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>7485950</v>
+        <v>7485900</v>
       </c>
       <c r="L83" s="5" t="n">
         <v>16785</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -14532,34 +14532,34 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>10089000</v>
+        <v>8777400</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>21375</v>
+        <v>18596</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K206" s="5" t="n">
-        <v>8575650</v>
+        <v>8777400</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>18169</v>
+        <v>18596</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
@@ -29110,34 +29110,34 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
-        <v>10667000</v>
+        <v>9066900</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>19255</v>
+        <v>16366</v>
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K421" s="5" t="n">
-        <v>9066950</v>
+        <v>9066900</v>
       </c>
       <c r="L421" s="5" t="n">
         <v>16366</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N421" s="3" t="inlineStr">
@@ -31539,7 +31539,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -34284,34 +34284,34 @@
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
-        <v>8759000</v>
+        <v>7445100</v>
       </c>
       <c r="I498" s="5" t="n">
-        <v>19336</v>
+        <v>16435</v>
       </c>
       <c r="J498" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K498" s="5" t="n">
-        <v>7445150</v>
+        <v>7445100</v>
       </c>
       <c r="L498" s="5" t="n">
         <v>16435</v>
       </c>
       <c r="M498" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N498" s="3" t="inlineStr">
@@ -48228,34 +48228,34 @@
       </c>
       <c r="F702" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G702" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H702" s="5" t="n">
-        <v>8687000</v>
+        <v>7383900</v>
       </c>
       <c r="I702" s="5" t="n">
-        <v>19521</v>
+        <v>16593</v>
       </c>
       <c r="J702" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K702" s="5" t="n">
-        <v>7383950</v>
+        <v>7383900</v>
       </c>
       <c r="L702" s="5" t="n">
         <v>16593</v>
       </c>
       <c r="M702" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N702" s="3" t="inlineStr">
@@ -79848,23 +79848,23 @@
       </c>
       <c r="F1176" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H1176" s="5" t="n">
-        <v>6982000</v>
+        <v>5934700</v>
       </c>
       <c r="I1176" s="5" t="n">
-        <v>20121</v>
+        <v>17103</v>
       </c>
       <c r="J1176" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1176" s="5" t="n">
@@ -79875,7 +79875,7 @@
       </c>
       <c r="M1176" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1176" s="3" t="inlineStr">
@@ -87425,7 +87425,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87435,7 +87435,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88256,12 +88256,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$881万
-$19,747/呎
-(在售)</t>
+$749万
+$16,785/呎
+(26年-09月-26日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -88989,7 +88989,7 @@
           <t>A | 472呎 (2房)
 $867万
 $18,369/呎
-(26年-09月-07日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -89360,12 +89360,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B45" s="22" t="inlineStr">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1009万
-$21,375/呎
-(在售)</t>
+$878万
+$18,596/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -90180,7 +90180,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90190,7 +90190,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -91529,12 +91529,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1067万
-$19,255/呎
-(在售)</t>
+$907万
+$16,366/呎
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -91864,7 +91864,7 @@
           <t>D | 554呎 (2房)
 $899万
 $16,221/呎
-(26年-08月-27日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -92252,12 +92252,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$876万
-$19,336/呎
-(在售)</t>
+$745万
+$16,435/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr">
@@ -93387,7 +93387,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93397,7 +93397,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94265,12 +94265,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$869万
-$19,521/呎
-(在售)</t>
+$738万
+$16,593/呎
+(26年-09月-26日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -96143,7 +96143,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96153,7 +96153,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -98768,12 +98768,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G45" s="22" t="inlineStr">
+      <c r="G45" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$698万
-$20,121/呎
-(在售)</t>
+$593万
+$17,103/呎
+(26年-09月-26日)</t>
         </is>
       </c>
       <c r="H45" s="23" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -6709,7 +6709,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -12902,34 +12902,34 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>10191000</v>
+        <v>8662300</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>21591</v>
+        <v>18352</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K181" s="5" t="n">
-        <v>8662350</v>
+        <v>8662300</v>
       </c>
       <c r="L181" s="5" t="n">
         <v>18352</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -33072,34 +33072,34 @@
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
-        <v>8811000</v>
+        <v>7489300</v>
       </c>
       <c r="I480" s="5" t="n">
-        <v>19450</v>
+        <v>16533</v>
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K480" s="5" t="n">
-        <v>7489350</v>
+        <v>7489300</v>
       </c>
       <c r="L480" s="5" t="n">
         <v>16533</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N480" s="3" t="inlineStr">
@@ -34688,34 +34688,34 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
-        <v>8759000</v>
+        <v>7445100</v>
       </c>
       <c r="I504" s="5" t="n">
-        <v>19336</v>
+        <v>16435</v>
       </c>
       <c r="J504" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K504" s="5" t="n">
-        <v>7445150</v>
+        <v>7445100</v>
       </c>
       <c r="L504" s="5" t="n">
         <v>16435</v>
       </c>
       <c r="M504" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N504" s="3" t="inlineStr">
@@ -48290,34 +48290,34 @@
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G703" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H703" s="5" t="n">
-        <v>9275000</v>
+        <v>7883700</v>
       </c>
       <c r="I703" s="5" t="n">
-        <v>19006</v>
+        <v>16155</v>
       </c>
       <c r="J703" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K703" s="5" t="n">
-        <v>7883750</v>
+        <v>7883700</v>
       </c>
       <c r="L703" s="5" t="n">
         <v>16155</v>
       </c>
       <c r="M703" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N703" s="3" t="inlineStr">
@@ -48492,23 +48492,23 @@
       </c>
       <c r="F706" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G706" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H706" s="5" t="n">
-        <v>8820000</v>
+        <v>7497000</v>
       </c>
       <c r="I706" s="5" t="n">
-        <v>19009</v>
+        <v>16157</v>
       </c>
       <c r="J706" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K706" s="5" t="n">
@@ -48519,7 +48519,7 @@
       </c>
       <c r="M706" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N706" s="3" t="inlineStr">
@@ -49475,7 +49475,7 @@
       </c>
       <c r="G721" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H721" s="5" t="n">
@@ -49920,23 +49920,23 @@
       </c>
       <c r="F728" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G728" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H728" s="5" t="n">
-        <v>9184000</v>
+        <v>7806400</v>
       </c>
       <c r="I728" s="5" t="n">
-        <v>18820</v>
+        <v>15997</v>
       </c>
       <c r="J728" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K728" s="5" t="n">
@@ -49947,7 +49947,7 @@
       </c>
       <c r="M728" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N728" s="3" t="inlineStr">
@@ -50246,34 +50246,34 @@
       </c>
       <c r="F733" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G733" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H733" s="5" t="n">
-        <v>9165000</v>
+        <v>7790200</v>
       </c>
       <c r="I733" s="5" t="n">
-        <v>18781</v>
+        <v>15964</v>
       </c>
       <c r="J733" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K733" s="5" t="n">
-        <v>7790250</v>
+        <v>7790200</v>
       </c>
       <c r="L733" s="5" t="n">
         <v>15964</v>
       </c>
       <c r="M733" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N733" s="3" t="inlineStr">
@@ -50453,7 +50453,7 @@
       </c>
       <c r="G736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H736" s="5" t="n">
@@ -51493,7 +51493,7 @@
       </c>
       <c r="G752" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H752" s="5" t="n">
@@ -51881,7 +51881,7 @@
       </c>
       <c r="G758" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H758" s="5" t="n">
@@ -52145,7 +52145,7 @@
       </c>
       <c r="G762" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H762" s="5" t="n">
@@ -54856,38 +54856,30 @@
       </c>
       <c r="F804" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G804" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H804" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I804" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H804" s="5" t="n">
+        <v>10970000</v>
+      </c>
+      <c r="I804" s="5" t="n">
+        <v>18223</v>
       </c>
       <c r="J804" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K804" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L804" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K804" s="5" t="n">
+        <v>10970000</v>
+      </c>
+      <c r="L804" s="5" t="n">
+        <v>18223</v>
       </c>
       <c r="M804" s="3" t="inlineStr">
         <is>
@@ -54896,7 +54888,7 @@
       </c>
       <c r="N804" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -59875,7 +59867,7 @@
       </c>
       <c r="G881" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H881" s="5" t="n">
@@ -74541,7 +74533,7 @@
       </c>
       <c r="G1096" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H1096" s="5" t="n">
@@ -76128,34 +76120,34 @@
       </c>
       <c r="F1120" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H1120" s="5" t="n">
-        <v>7067000</v>
+        <v>6006900</v>
       </c>
       <c r="I1120" s="5" t="n">
-        <v>20366</v>
+        <v>17311</v>
       </c>
       <c r="J1120" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1120" s="5" t="n">
-        <v>6006950</v>
+        <v>6006900</v>
       </c>
       <c r="L1120" s="5" t="n">
         <v>17311</v>
       </c>
       <c r="M1120" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1120" s="3" t="inlineStr">
@@ -77254,38 +77246,30 @@
       </c>
       <c r="F1137" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1137" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1137" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H1137" s="5" t="n">
+        <v>10578000</v>
+      </c>
+      <c r="I1137" s="5" t="n">
+        <v>17838</v>
       </c>
       <c r="J1137" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1137" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1137" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1137" s="5" t="n">
+        <v>10578000</v>
+      </c>
+      <c r="L1137" s="5" t="n">
+        <v>17838</v>
       </c>
       <c r="M1137" s="3" t="inlineStr">
         <is>
@@ -77294,7 +77278,7 @@
       </c>
       <c r="N1137" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -77518,34 +77502,34 @@
       </c>
       <c r="F1141" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H1141" s="5" t="n">
-        <v>7035000</v>
+        <v>5979700</v>
       </c>
       <c r="I1141" s="5" t="n">
-        <v>20274</v>
+        <v>17233</v>
       </c>
       <c r="J1141" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1141" s="5" t="n">
-        <v>5979750</v>
+        <v>5979700</v>
       </c>
       <c r="L1141" s="5" t="n">
         <v>17233</v>
       </c>
       <c r="M1141" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1141" s="3" t="inlineStr">
@@ -81534,38 +81518,30 @@
       </c>
       <c r="F1201" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1201" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1201" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H1201" s="5" t="n">
+        <v>14957000</v>
+      </c>
+      <c r="I1201" s="5" t="n">
+        <v>19102</v>
       </c>
       <c r="J1201" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1201" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1201" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1201" s="5" t="n">
+        <v>14957000</v>
+      </c>
+      <c r="L1201" s="5" t="n">
+        <v>19102</v>
       </c>
       <c r="M1201" s="3" t="inlineStr">
         <is>
@@ -81574,7 +81550,7 @@
       </c>
       <c r="N1201" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -87425,7 +87401,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87435,7 +87411,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88308,7 +88284,7 @@
           <t>D | 446呎 (2房)
 $740万
 $16,592/呎
-(26年-09月-08日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -88449,7 +88425,7 @@
           <t>D | 446呎 (2房)
 $737万
 $16,518/呎
-(26年-09月-13日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -88590,7 +88566,7 @@
           <t>D | 446呎 (2房)
 $733万
 $16,443/呎
-(26年-09月-07日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -88660,7 +88636,7 @@
           <t>A | 472呎 (2房)
 $879万
 $18,630/呎
-(26年-09月-13日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -89125,12 +89101,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1019万
-$21,591/呎
-(在售)</t>
+$866万
+$18,352/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
@@ -89647,7 +89623,7 @@
           <t>A | 472呎 (2房)
 $842万
 $17,828/呎
-(26年-09月-11日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
@@ -90180,17 +90156,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -92087,12 +92063,12 @@
 (26年-08月-11日)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$881万
-$19,450/呎
-(在售)</t>
+$749万
+$16,533/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -92307,12 +92283,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$876万
-$19,336/呎
-(在售)</t>
+$745万
+$16,435/呎
+(26年-10月-01日)</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
@@ -93387,7 +93363,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93397,7 +93373,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94257,12 +94233,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$928万
-$19,006/呎
-(在售)</t>
+$788万
+$16,155/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -94320,7 +94296,54 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$750万
+$16,157/呎
+(26年-10月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 472呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 602呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 488呎 (2房)
+$926万
+$18,967/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 445呎 (2房)
+$867万
+$19,492/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
 $882万
@@ -94329,53 +94352,6 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 472呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>B | 602呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>C | 488呎 (2房)
-$926万
-$18,967/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>D | 445呎 (2房)
-$867万
-$19,492/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$882万
-$19,009/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
@@ -94466,7 +94442,7 @@
           <t>E | 464呎 (2房)
 $746万
 $16,084/呎
-(26年-09月-08日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -94492,12 +94468,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$918万
-$18,820/呎
-(在售)</t>
+$781万
+$15,997/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -94539,12 +94515,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$916万
-$18,781/呎
-(在售)</t>
+$779万
+$15,964/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -94607,7 +94583,7 @@
           <t>E | 464呎 (2房)
 $743万
 $16,011/呎
-(26年-09月-03日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -94740,7 +94716,7 @@
           <t>D | 445呎 (2房)
 $745万
 $16,731/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
@@ -94779,7 +94755,7 @@
           <t>C | 488呎 (2房)
 $773万
 $15,836/呎
-(26年-09月-17日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -94834,7 +94810,7 @@
           <t>D | 445呎 (2房)
 $725万
 $16,297/呎
-(26年-09月-09日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
@@ -95189,12 +95165,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
-招标单位
--
-(在售)</t>
+$1097万
+$18,223/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
@@ -95970,7 +95946,7 @@
           <t>E | 464呎 (2房)
 $728万
 $15,690/呎
-(26年-09月-04日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -96143,7 +96119,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96153,7 +96129,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -97985,7 +97961,7 @@
           <t>B | 783呎 (3房)
 $1547万
 $19,762/呎
-(26年-09月-09日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -98264,12 +98240,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$707万
-$20,366/呎
-(在售)</t>
+$601万
+$17,311/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
@@ -98366,12 +98342,12 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
+$1058万
+$17,838/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -98453,12 +98429,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$704万
-$20,274/呎
-(在售)</t>
+$598万
+$17,233/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H40" s="23" t="inlineStr">
@@ -98925,12 +98901,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C48" s="22" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1496万
+$19,102/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -28706,34 +28706,34 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
-        <v>10684000</v>
+        <v>9295000</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>19285</v>
+        <v>16778</v>
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K415" s="5" t="n">
-        <v>9081400</v>
+        <v>9295000</v>
       </c>
       <c r="L415" s="5" t="n">
-        <v>16392</v>
+        <v>16778</v>
       </c>
       <c r="M415" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N415" s="3" t="inlineStr">
@@ -29519,14 +29519,14 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
-        <v>9053000</v>
+        <v>9053300</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>16341</v>
+        <v>16342</v>
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
@@ -29534,10 +29534,10 @@
         </is>
       </c>
       <c r="K427" s="5" t="n">
-        <v>9053000</v>
+        <v>9053300</v>
       </c>
       <c r="L427" s="5" t="n">
-        <v>16341</v>
+        <v>16342</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
       </c>
       <c r="G701" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H701" s="5" t="n">
@@ -48818,23 +48818,23 @@
       </c>
       <c r="F711" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G711" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H711" s="5" t="n">
-        <v>8820000</v>
+        <v>7497000</v>
       </c>
       <c r="I711" s="5" t="n">
-        <v>19009</v>
+        <v>16157</v>
       </c>
       <c r="J711" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K711" s="5" t="n">
@@ -48845,7 +48845,7 @@
       </c>
       <c r="M711" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N711" s="3" t="inlineStr">
@@ -49594,34 +49594,34 @@
       </c>
       <c r="F723" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G723" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H723" s="5" t="n">
-        <v>9201000</v>
+        <v>7820800</v>
       </c>
       <c r="I723" s="5" t="n">
-        <v>18855</v>
+        <v>16026</v>
       </c>
       <c r="J723" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K723" s="5" t="n">
-        <v>7820850</v>
+        <v>7820800</v>
       </c>
       <c r="L723" s="5" t="n">
         <v>16026</v>
       </c>
       <c r="M723" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N723" s="3" t="inlineStr">
@@ -51162,34 +51162,34 @@
       </c>
       <c r="F747" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G747" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H747" s="5" t="n">
-        <v>8571000</v>
+        <v>7285300</v>
       </c>
       <c r="I747" s="5" t="n">
-        <v>19261</v>
+        <v>16371</v>
       </c>
       <c r="J747" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K747" s="5" t="n">
-        <v>7285350</v>
+        <v>7285300</v>
       </c>
       <c r="L747" s="5" t="n">
-        <v>16372</v>
+        <v>16371</v>
       </c>
       <c r="M747" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N747" s="3" t="inlineStr">
@@ -56136,38 +56136,30 @@
       </c>
       <c r="F824" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G824" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H824" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I824" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H824" s="5" t="n">
+        <v>10840000</v>
+      </c>
+      <c r="I824" s="5" t="n">
+        <v>18007</v>
       </c>
       <c r="J824" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K824" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L824" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K824" s="5" t="n">
+        <v>10840000</v>
+      </c>
+      <c r="L824" s="5" t="n">
+        <v>18007</v>
       </c>
       <c r="M824" s="3" t="inlineStr">
         <is>
@@ -56176,7 +56168,7 @@
       </c>
       <c r="N824" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -73122,38 +73114,30 @@
       </c>
       <c r="F1075" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1075" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1075" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1075" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H1075" s="5" t="n">
+        <v>15157000</v>
+      </c>
+      <c r="I1075" s="5" t="n">
+        <v>19358</v>
       </c>
       <c r="J1075" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1075" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1075" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1075" s="5" t="n">
+        <v>15157000</v>
+      </c>
+      <c r="L1075" s="5" t="n">
+        <v>19358</v>
       </c>
       <c r="M1075" s="3" t="inlineStr">
         <is>
@@ -73162,7 +73146,7 @@
       </c>
       <c r="N1075" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -74999,7 +74983,7 @@
       </c>
       <c r="G1103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H1103" s="5" t="n">
@@ -77973,7 +77957,7 @@
       </c>
       <c r="G1148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H1148" s="5" t="n">
@@ -80303,7 +80287,7 @@
       </c>
       <c r="G1183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H1183" s="5" t="n">
@@ -88331,7 +88315,7 @@
           <t>D | 446呎 (2房)
 $739万
 $16,567/呎
-(26年-09月-18日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -88871,7 +88855,7 @@
           <t>A | 472呎 (2房)
 $891万
 $18,876/呎
-(26年-09月-19日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -89153,7 +89137,7 @@
           <t>A | 472呎 (2房)
 $880万
 $18,651/呎
-(26年-09月-13日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -90156,7 +90140,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90166,7 +90150,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -91450,12 +91434,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1068万
-$19,285/呎
-(在售)</t>
+$930万
+$16,778/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -91564,8 +91548,8 @@
         <is>
           <t>D | 554呎 (2房)
 $905万
-$16,341/呎
-(26年-09月-18日)</t>
+$16,342/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -93363,7 +93347,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93373,7 +93357,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94254,7 +94238,7 @@
           <t>E | 464呎 (2房)
 $751万
 $16,181/呎
-(26年-09月-14日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -94343,12 +94327,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
-$882万
-$19,009/呎
-(在售)</t>
+$750万
+$16,157/呎
+(26年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -94421,12 +94405,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$920万
-$18,855/呎
-(在售)</t>
+$782万
+$16,026/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -94664,12 +94648,12 @@
 (26年-09月-22日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$857万
-$19,261/呎
-(在售)</t>
+$729万
+$16,371/呎
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -95353,12 +95337,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
-招标单位
--
-(在售)</t>
+$1084万
+$18,007/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
@@ -96119,7 +96103,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96129,7 +96113,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -97767,12 +97751,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1516万
+$19,358/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -98024,7 +98008,7 @@
           <t>B | 783呎 (3房)
 $1549万
 $19,783/呎
-(26年-09月-18日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -98497,7 +98481,7 @@
           <t>F | 347呎 (1房)
 $611万
 $17,613/呎
-(26年-09月-21日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="H41" s="23" t="inlineStr">
@@ -98812,7 +98796,7 @@
           <t>F | 347呎 (1房)
 $606万
 $17,455/呎
-(26年-09月-11日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="H46" s="23" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -14211,7 +14211,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -26282,34 +26282,34 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
-        <v>10833000</v>
+        <v>9424700</v>
       </c>
       <c r="I379" s="5" t="n">
-        <v>19554</v>
+        <v>17012</v>
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K379" s="5" t="n">
-        <v>9208050</v>
+        <v>9424700</v>
       </c>
       <c r="L379" s="5" t="n">
-        <v>16621</v>
+        <v>17012</v>
       </c>
       <c r="M379" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N379" s="3" t="inlineStr">
@@ -26414,38 +26414,30 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H381" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I381" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H381" s="5" t="n">
+        <v>12611000</v>
+      </c>
+      <c r="I381" s="5" t="n">
+        <v>20081</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K381" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L381" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K381" s="5" t="n">
+        <v>12611000</v>
+      </c>
+      <c r="L381" s="5" t="n">
+        <v>20081</v>
       </c>
       <c r="M381" s="3" t="inlineStr">
         <is>
@@ -26454,7 +26446,7 @@
       </c>
       <c r="N381" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29923,7 +29915,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -32280,34 +32272,34 @@
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
-        <v>8846000</v>
+        <v>7696000</v>
       </c>
       <c r="I468" s="5" t="n">
-        <v>19528</v>
+        <v>16989</v>
       </c>
       <c r="J468" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K468" s="5" t="n">
-        <v>7519100</v>
+        <v>7696000</v>
       </c>
       <c r="L468" s="5" t="n">
-        <v>16598</v>
+        <v>16989</v>
       </c>
       <c r="M468" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N468" s="3" t="inlineStr">
@@ -32676,23 +32668,23 @@
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
-        <v>8828000</v>
+        <v>7503800</v>
       </c>
       <c r="I474" s="5" t="n">
-        <v>19488</v>
+        <v>16565</v>
       </c>
       <c r="J474" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K474" s="5" t="n">
@@ -32703,7 +32695,7 @@
       </c>
       <c r="M474" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N474" s="3" t="inlineStr">
@@ -32875,7 +32867,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -34755,14 +34747,14 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
-        <v>9055800</v>
+        <v>8847600</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>16346</v>
+        <v>15970</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -34770,10 +34762,10 @@
         </is>
       </c>
       <c r="K505" s="5" t="n">
-        <v>9055800</v>
+        <v>8847600</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>16346</v>
+        <v>15970</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
@@ -47840,34 +47832,34 @@
       </c>
       <c r="F696" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G696" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H696" s="5" t="n">
-        <v>8846000</v>
+        <v>7696000</v>
       </c>
       <c r="I696" s="5" t="n">
-        <v>19065</v>
+        <v>16586</v>
       </c>
       <c r="J696" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K696" s="5" t="n">
-        <v>7519100</v>
+        <v>7696000</v>
       </c>
       <c r="L696" s="5" t="n">
-        <v>16205</v>
+        <v>16586</v>
       </c>
       <c r="M696" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N696" s="3" t="inlineStr">
@@ -47964,23 +47956,23 @@
       </c>
       <c r="F698" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G698" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H698" s="5" t="n">
-        <v>9294000</v>
+        <v>7899900</v>
       </c>
       <c r="I698" s="5" t="n">
-        <v>19045</v>
+        <v>16188</v>
       </c>
       <c r="J698" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K698" s="5" t="n">
@@ -47991,7 +47983,7 @@
       </c>
       <c r="M698" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N698" s="3" t="inlineStr">
@@ -48616,34 +48608,34 @@
       </c>
       <c r="F708" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G708" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H708" s="5" t="n">
-        <v>9256000</v>
+        <v>8052700</v>
       </c>
       <c r="I708" s="5" t="n">
-        <v>18967</v>
+        <v>16501</v>
       </c>
       <c r="J708" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K708" s="5" t="n">
-        <v>7867600</v>
+        <v>8052700</v>
       </c>
       <c r="L708" s="5" t="n">
-        <v>16122</v>
+        <v>16501</v>
       </c>
       <c r="M708" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N708" s="3" t="inlineStr">
@@ -48880,23 +48872,23 @@
       </c>
       <c r="F712" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G712" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H712" s="5" t="n">
-        <v>8674000</v>
+        <v>7372900</v>
       </c>
       <c r="I712" s="5" t="n">
-        <v>19492</v>
+        <v>16568</v>
       </c>
       <c r="J712" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K712" s="5" t="n">
@@ -48907,7 +48899,7 @@
       </c>
       <c r="M712" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N712" s="3" t="inlineStr">
@@ -50903,7 +50895,7 @@
       </c>
       <c r="G743" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H743" s="5" t="n">
@@ -73580,38 +73572,30 @@
       </c>
       <c r="F1082" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1082" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1082" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1082" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H1082" s="5" t="n">
+        <v>15127000</v>
+      </c>
+      <c r="I1082" s="5" t="n">
+        <v>19319</v>
       </c>
       <c r="J1082" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1082" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1082" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1082" s="5" t="n">
+        <v>15127000</v>
+      </c>
+      <c r="L1082" s="5" t="n">
+        <v>19319</v>
       </c>
       <c r="M1082" s="3" t="inlineStr">
         <is>
@@ -73620,7 +73604,7 @@
       </c>
       <c r="N1082" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -77028,23 +77012,23 @@
       </c>
       <c r="F1134" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="H1134" s="5" t="n">
-        <v>7046000</v>
+        <v>5989100</v>
       </c>
       <c r="I1134" s="5" t="n">
-        <v>20305</v>
+        <v>17260</v>
       </c>
       <c r="J1134" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1134" s="5" t="n">
@@ -77055,7 +77039,7 @@
       </c>
       <c r="M1134" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1134" s="3" t="inlineStr">
@@ -78889,7 +78873,7 @@
       </c>
       <c r="G1162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H1162" s="5" t="n">
@@ -79355,7 +79339,7 @@
       </c>
       <c r="G1169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H1169" s="5" t="n">
@@ -89278,7 +89262,7 @@
           <t>A | 472呎 (2房)
 $859万
 $18,205/呎
-(26年-09月-22日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
@@ -89795,7 +89779,7 @@
           <t>A | 472呎 (2房)
 $835万
 $17,686/呎
-(26年-09月-21日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -90140,7 +90124,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90150,7 +90134,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -91088,12 +91072,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-招标单位
--
-(在售)</t>
+$1261万
+$20,081/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -91104,12 +91088,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$1083万
-$19,554/呎
-(在售)</t>
+$942万
+$17,012/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -91604,7 +91588,7 @@
           <t>D | 554呎 (2房)
 $904万
 $16,317/呎
-(26年-09月-23日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -91937,12 +91921,12 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$885万
-$19,528/呎
-(在售)</t>
+$770万
+$16,989/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -91973,7 +91957,7 @@
           <t>B | 628呎 (3房)
 $1252万
 $19,936/呎
-(26年-09月-23日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -91992,12 +91976,12 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$883万
-$19,488/呎
-(在售)</t>
+$750万
+$16,565/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
@@ -92262,9 +92246,9 @@
       <c r="E42" s="23" t="inlineStr">
         <is>
           <t>D | 554呎 (2房)
-$906万
-$16,346/呎
-(26年-08月-14日)</t>
+$885万
+$15,970/呎
+(26年-07月-25日)</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
@@ -93347,7 +93331,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93357,7 +93341,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94170,12 +94154,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$929万
-$19,045/呎
-(在售)</t>
+$790万
+$16,188/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -94186,12 +94170,12 @@
 (26年-08月-20日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 464呎 (2房)
-$885万
-$19,065/呎
-(在售)</t>
+$770万
+$16,586/呎
+(26年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -94264,7 +94248,54 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 488呎 (2房)
+$805万
+$16,501/呎
+(26年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 445呎 (2房)
+$867万
+$19,492/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 464呎 (2房)
+$750万
+$16,157/呎
+(26年-10月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 472呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 602呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
 $926万
@@ -94272,59 +94303,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$867万
-$19,492/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>E | 464呎 (2房)
-$750万
-$16,157/呎
-(26年-10月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 472呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>B | 602呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>C | 488呎 (2房)
-$926万
-$18,967/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>D | 445呎 (2房)
-$867万
-$19,492/呎
-(在售)</t>
+$737万
+$16,568/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -94598,7 +94582,7 @@
           <t>C | 488呎 (2房)
 $794万
 $16,273/呎
-(26年-09月-19日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -96103,7 +96087,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>118</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96113,7 +96097,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -97814,12 +97798,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1513万
+$19,319/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -98350,12 +98334,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G39" s="22" t="inlineStr">
+      <c r="G39" s="23" t="inlineStr">
         <is>
           <t>F | 347呎 (1房)
-$705万
-$20,305/呎
-(在售)</t>
+$599万
+$17,260/呎
+(26年-10月-11日)</t>
         </is>
       </c>
       <c r="H39" s="23" t="inlineStr">
@@ -98607,7 +98591,7 @@
           <t>F | 347呎 (1房)
 $609万
 $17,560/呎
-(26年-09月-15日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="H43" s="23" t="inlineStr">
@@ -98670,7 +98654,7 @@
           <t>F | 347呎 (1房)
 $594万
 $17,130/呎
-(26年-09月-14日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="H44" s="23" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -12907,7 +12907,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -28299,7 +28299,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -31868,23 +31868,23 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
-        <v>8864000</v>
+        <v>7534400</v>
       </c>
       <c r="I462" s="5" t="n">
-        <v>19567</v>
+        <v>16632</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K462" s="5" t="n">
@@ -31895,7 +31895,7 @@
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N462" s="3" t="inlineStr">
@@ -33473,7 +33473,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -33877,7 +33877,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -49141,7 +49141,7 @@
       </c>
       <c r="G716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H716" s="5" t="n">
@@ -69322,38 +69322,30 @@
       </c>
       <c r="F1019" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1019" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1019" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1019" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H1019" s="5" t="n">
+        <v>15402000</v>
+      </c>
+      <c r="I1019" s="5" t="n">
+        <v>19670</v>
       </c>
       <c r="J1019" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1019" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1019" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1019" s="5" t="n">
+        <v>15402000</v>
+      </c>
+      <c r="L1019" s="5" t="n">
+        <v>19670</v>
       </c>
       <c r="M1019" s="3" t="inlineStr">
         <is>
@@ -69362,7 +69354,7 @@
       </c>
       <c r="N1019" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -72158,38 +72150,30 @@
       </c>
       <c r="F1061" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1061" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1061" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1061" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H1061" s="5" t="n">
+        <v>15218000</v>
+      </c>
+      <c r="I1061" s="5" t="n">
+        <v>19436</v>
       </c>
       <c r="J1061" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1061" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1061" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1061" s="5" t="n">
+        <v>15218000</v>
+      </c>
+      <c r="L1061" s="5" t="n">
+        <v>19436</v>
       </c>
       <c r="M1061" s="3" t="inlineStr">
         <is>
@@ -72198,7 +72182,7 @@
       </c>
       <c r="N1061" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -76093,7 +76077,7 @@
       </c>
       <c r="G1120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H1120" s="5" t="n">
@@ -79805,7 +79789,7 @@
       </c>
       <c r="G1176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H1176" s="5" t="n">
@@ -89074,7 +89058,7 @@
           <t>A | 472呎 (2房)
 $866万
 $18,352/呎
-(26年-09月-28日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
@@ -89309,7 +89293,7 @@
           <t>A | 472呎 (2房)
 $878万
 $18,596/呎
-(26年-09月-27日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -90124,7 +90108,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90134,7 +90118,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -91368,7 +91352,7 @@
           <t>D | 554呎 (2房)
 $909万
 $16,415/呎
-(26年-09月-22日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -91866,12 +91850,12 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$886万
-$19,567/呎
-(在售)</t>
+$753万
+$16,632/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -92091,7 +92075,7 @@
           <t>E | 453呎 (2房)
 $747万
 $16,499/呎
-(26年-09月-22日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
@@ -92146,7 +92130,7 @@
           <t>E | 453呎 (2房)
 $746万
 $16,467/呎
-(26年-09月-22日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
@@ -94363,7 +94347,7 @@
           <t>E | 464呎 (2房)
 $747万
 $16,108/呎
-(26年-09月-21日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -96087,7 +96071,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96097,7 +96081,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -97231,12 +97215,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1540万
+$19,670/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -97609,12 +97593,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1522万
+$19,436/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -98213,7 +98197,7 @@
           <t>F | 347呎 (1房)
 $601万
 $17,311/呎
-(26年-09月-28日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="H37" s="23" t="inlineStr">
@@ -98717,7 +98701,7 @@
           <t>F | 347呎 (1房)
 $593万
 $17,103/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="H45" s="23" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -29107,7 +29107,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -50569,7 +50569,7 @@
       </c>
       <c r="G738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H738" s="5" t="n">
@@ -77459,7 +77459,7 @@
       </c>
       <c r="G1141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H1141" s="5" t="n">
@@ -88189,7 +88189,7 @@
           <t>D | 446呎 (2房)
 $749万
 $16,785/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -91462,7 +91462,7 @@
           <t>D | 554呎 (2房)
 $907万
 $16,366/呎
-(26年-09月-25日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -92185,7 +92185,7 @@
           <t>E | 453呎 (2房)
 $745万
 $16,435/呎
-(26年-09月-27日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr">
@@ -94519,7 +94519,7 @@
           <t>C | 488呎 (2房)
 $777万
 $15,931/呎
-(26年-09月-21日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -98386,7 +98386,7 @@
           <t>F | 347呎 (1房)
 $598万
 $17,233/呎
-(26年-09月-30日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="H40" s="23" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -12576,34 +12576,34 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
-        <v>10211000</v>
+        <v>8679300</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>21633</v>
+        <v>18388</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K176" s="5" t="n">
-        <v>8679350</v>
+        <v>8679300</v>
       </c>
       <c r="L176" s="5" t="n">
         <v>18388</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
@@ -28232,34 +28232,34 @@
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
-        <v>9025000</v>
+        <v>7671200</v>
       </c>
       <c r="I408" s="5" t="n">
-        <v>19923</v>
+        <v>16934</v>
       </c>
       <c r="J408" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K408" s="5" t="n">
-        <v>7671250</v>
+        <v>7671200</v>
       </c>
       <c r="L408" s="5" t="n">
         <v>16934</v>
       </c>
       <c r="M408" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N408" s="3" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -29515,10 +29515,10 @@
         </is>
       </c>
       <c r="H427" s="5" t="n">
-        <v>9053300</v>
+        <v>9053000</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>16342</v>
+        <v>16341</v>
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
@@ -29526,10 +29526,10 @@
         </is>
       </c>
       <c r="K427" s="5" t="n">
-        <v>9053300</v>
+        <v>9053000</v>
       </c>
       <c r="L427" s="5" t="n">
-        <v>16342</v>
+        <v>16341</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
@@ -30656,23 +30656,23 @@
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
-        <v>8918000</v>
+        <v>7580300</v>
       </c>
       <c r="I444" s="5" t="n">
-        <v>19687</v>
+        <v>16734</v>
       </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K444" s="5" t="n">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="M444" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N444" s="3" t="inlineStr">
@@ -31060,23 +31060,23 @@
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
-        <v>8918000</v>
+        <v>7580300</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>19687</v>
+        <v>16734</v>
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K450" s="5" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N450" s="3" t="inlineStr">
@@ -31464,34 +31464,34 @@
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
-        <v>8881000</v>
+        <v>7548800</v>
       </c>
       <c r="I456" s="5" t="n">
-        <v>19605</v>
+        <v>16664</v>
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K456" s="5" t="n">
-        <v>7548850</v>
+        <v>7548800</v>
       </c>
       <c r="L456" s="5" t="n">
         <v>16664</v>
       </c>
       <c r="M456" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N456" s="3" t="inlineStr">
@@ -33069,7 +33069,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -34685,7 +34685,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -41144,34 +41144,34 @@
       </c>
       <c r="F600" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G600" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="H600" s="5" t="n">
-        <v>8551000</v>
+        <v>7268300</v>
       </c>
       <c r="I600" s="5" t="n">
-        <v>18876</v>
+        <v>16045</v>
       </c>
       <c r="J600" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K600" s="5" t="n">
-        <v>7268350</v>
+        <v>7268300</v>
       </c>
       <c r="L600" s="5" t="n">
         <v>16045</v>
       </c>
       <c r="M600" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N600" s="3" t="inlineStr">
@@ -41548,34 +41548,34 @@
       </c>
       <c r="F606" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G606" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H606" s="5" t="n">
-        <v>8516000</v>
+        <v>7408900</v>
       </c>
       <c r="I606" s="5" t="n">
-        <v>18799</v>
+        <v>16355</v>
       </c>
       <c r="J606" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K606" s="5" t="n">
-        <v>7238600</v>
+        <v>7408900</v>
       </c>
       <c r="L606" s="5" t="n">
-        <v>15979</v>
+        <v>16355</v>
       </c>
       <c r="M606" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N606" s="3" t="inlineStr">
@@ -48225,7 +48225,7 @@
       </c>
       <c r="G702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H702" s="5" t="n">
@@ -48287,7 +48287,7 @@
       </c>
       <c r="G703" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H703" s="5" t="n">
@@ -48489,7 +48489,7 @@
       </c>
       <c r="G706" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H706" s="5" t="n">
@@ -48815,7 +48815,7 @@
       </c>
       <c r="G711" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H711" s="5" t="n">
@@ -48934,23 +48934,23 @@
       </c>
       <c r="F713" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G713" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="H713" s="5" t="n">
-        <v>9256000</v>
+        <v>7867600</v>
       </c>
       <c r="I713" s="5" t="n">
-        <v>18967</v>
+        <v>16122</v>
       </c>
       <c r="J713" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K713" s="5" t="n">
@@ -48961,7 +48961,7 @@
       </c>
       <c r="M713" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N713" s="3" t="inlineStr">
@@ -49260,23 +49260,23 @@
       </c>
       <c r="F718" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G718" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="H718" s="5" t="n">
-        <v>9220000</v>
+        <v>7837000</v>
       </c>
       <c r="I718" s="5" t="n">
-        <v>18893</v>
+        <v>16059</v>
       </c>
       <c r="J718" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K718" s="5" t="n">
@@ -49287,7 +49287,7 @@
       </c>
       <c r="M718" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N718" s="3" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="G728" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H728" s="5" t="n">
@@ -50243,7 +50243,7 @@
       </c>
       <c r="G733" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H733" s="5" t="n">
@@ -50828,23 +50828,23 @@
       </c>
       <c r="F742" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G742" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H742" s="5" t="n">
-        <v>8584000</v>
+        <v>7296400</v>
       </c>
       <c r="I742" s="5" t="n">
-        <v>19290</v>
+        <v>16396</v>
       </c>
       <c r="J742" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K742" s="5" t="n">
@@ -50855,7 +50855,7 @@
       </c>
       <c r="M742" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N742" s="3" t="inlineStr">
@@ -54853,7 +54853,7 @@
       </c>
       <c r="G804" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H804" s="5" t="n">
@@ -55166,38 +55166,30 @@
       </c>
       <c r="F809" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G809" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H809" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I809" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H809" s="5" t="n">
+        <v>10927000</v>
+      </c>
+      <c r="I809" s="5" t="n">
+        <v>18151</v>
       </c>
       <c r="J809" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K809" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L809" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K809" s="5" t="n">
+        <v>10927000</v>
+      </c>
+      <c r="L809" s="5" t="n">
+        <v>18151</v>
       </c>
       <c r="M809" s="3" t="inlineStr">
         <is>
@@ -55206,7 +55198,7 @@
       </c>
       <c r="N809" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -56133,7 +56125,7 @@
       </c>
       <c r="G824" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H824" s="5" t="n">
@@ -68016,34 +68008,34 @@
       </c>
       <c r="F1000" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1000" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H1000" s="5" t="n">
-        <v>8829000</v>
+        <v>7504600</v>
       </c>
       <c r="I1000" s="5" t="n">
-        <v>19235</v>
+        <v>16350</v>
       </c>
       <c r="J1000" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1000" s="5" t="n">
-        <v>7504650</v>
+        <v>7504600</v>
       </c>
       <c r="L1000" s="5" t="n">
         <v>16350</v>
       </c>
       <c r="M1000" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1000" s="3" t="inlineStr">
@@ -68840,38 +68832,30 @@
       </c>
       <c r="F1012" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1012" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1012" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1012" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H1012" s="5" t="n">
+        <v>15432000</v>
+      </c>
+      <c r="I1012" s="5" t="n">
+        <v>19709</v>
       </c>
       <c r="J1012" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1012" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1012" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1012" s="5" t="n">
+        <v>15432000</v>
+      </c>
+      <c r="L1012" s="5" t="n">
+        <v>19709</v>
       </c>
       <c r="M1012" s="3" t="inlineStr">
         <is>
@@ -68880,7 +68864,7 @@
       </c>
       <c r="N1012" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -69788,38 +69772,30 @@
       </c>
       <c r="F1026" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1026" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1026" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1026" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H1026" s="5" t="n">
+        <v>15371000</v>
+      </c>
+      <c r="I1026" s="5" t="n">
+        <v>19631</v>
       </c>
       <c r="J1026" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1026" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1026" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1026" s="5" t="n">
+        <v>15371000</v>
+      </c>
+      <c r="L1026" s="5" t="n">
+        <v>19631</v>
       </c>
       <c r="M1026" s="3" t="inlineStr">
         <is>
@@ -69828,7 +69804,7 @@
       </c>
       <c r="N1026" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -73095,7 +73071,7 @@
       </c>
       <c r="G1075" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H1075" s="5" t="n">
@@ -73952,38 +73928,30 @@
       </c>
       <c r="F1088" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1088" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1088" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1088" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H1088" s="5" t="n">
+        <v>10465000</v>
+      </c>
+      <c r="I1088" s="5" t="n">
+        <v>17648</v>
       </c>
       <c r="J1088" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1088" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1088" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1088" s="5" t="n">
+        <v>10465000</v>
+      </c>
+      <c r="L1088" s="5" t="n">
+        <v>17648</v>
       </c>
       <c r="M1088" s="3" t="inlineStr">
         <is>
@@ -73992,7 +73960,7 @@
       </c>
       <c r="N1088" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -77203,7 +77171,7 @@
       </c>
       <c r="G1137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H1137" s="5" t="n">
@@ -80522,38 +80490,30 @@
       </c>
       <c r="F1187" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1187" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1187" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H1187" s="5" t="n">
+        <v>15313000</v>
+      </c>
+      <c r="I1187" s="5" t="n">
+        <v>19557</v>
       </c>
       <c r="J1187" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1187" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1187" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1187" s="5" t="n">
+        <v>15313000</v>
+      </c>
+      <c r="L1187" s="5" t="n">
+        <v>19557</v>
       </c>
       <c r="M1187" s="3" t="inlineStr">
         <is>
@@ -80562,7 +80522,7 @@
       </c>
       <c r="N1187" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -81475,7 +81435,7 @@
       </c>
       <c r="G1201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H1201" s="5" t="n">
@@ -87353,7 +87313,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87363,7 +87323,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -89006,12 +88966,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1021万
-$21,633/呎
-(在售)</t>
+$868万
+$18,388/呎
+(26年-10月-18日)</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -90108,7 +90068,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90118,7 +90078,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -91355,12 +91315,12 @@
 (26年-10月-14日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$902万
-$19,923/呎
-(在售)</t>
+$767万
+$16,934/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -91407,7 +91367,7 @@
           <t>D | 554呎 (2房)
 $930万
 $16,778/呎
-(26年-10月-06日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -91516,7 +91476,7 @@
         <is>
           <t>D | 554呎 (2房)
 $905万
-$16,342/呎
+$16,341/呎
 (26年-10月-08日)</t>
         </is>
       </c>
@@ -91685,12 +91645,12 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$892万
-$19,687/呎
-(在售)</t>
+$758万
+$16,734/呎
+(26年-10月-19日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -91740,12 +91700,12 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$892万
-$19,687/呎
-(在售)</t>
+$758万
+$16,734/呎
+(26年-10月-17日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -91795,12 +91755,12 @@
 (26年-09月-25日)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$888万
-$19,605/呎
-(在售)</t>
+$755万
+$16,664/呎
+(26年-10月-24日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -92020,7 +91980,7 @@
           <t>E | 453呎 (2房)
 $749万
 $16,533/呎
-(26年-10月-02日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -92240,7 +92200,7 @@
           <t>E | 453呎 (2房)
 $745万
 $16,435/呎
-(26年-10月-01日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
@@ -93115,12 +93075,12 @@
 (26年-09月-18日)</t>
         </is>
       </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="F58" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$855万
-$18,876/呎
-(在售)</t>
+$727万
+$16,045/呎
+(26年-10月-25日)</t>
         </is>
       </c>
       <c r="G58" s="20" t="inlineStr">
@@ -93170,12 +93130,12 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F59" s="22" t="inlineStr">
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$852万
-$18,799/呎
-(在售)</t>
+$741万
+$16,355/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="G59" s="20" t="inlineStr">
@@ -93315,7 +93275,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -93325,7 +93285,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>118</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -94190,7 +94150,7 @@
           <t>C | 488呎 (2房)
 $788万
 $16,155/呎
-(26年-09月-28日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -94198,7 +94158,7 @@
           <t>D | 445呎 (2房)
 $738万
 $16,593/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -94253,7 +94213,7 @@
           <t>E | 464呎 (2房)
 $750万
 $16,157/呎
-(26年-10月-01日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -94279,12 +94239,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$926万
-$18,967/呎
-(在售)</t>
+$787万
+$16,122/呎
+(26年-10月-25日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -94300,7 +94260,7 @@
           <t>E | 464呎 (2房)
 $750万
 $16,157/呎
-(26年-10月-05日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -94326,12 +94286,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 488呎 (2房)
-$922万
-$18,893/呎
-(在售)</t>
+$784万
+$16,059/呎
+(26年-10月-25日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -94425,7 +94385,7 @@
           <t>C | 488呎 (2房)
 $781万
 $15,997/呎
-(26年-10月-03日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -94472,7 +94432,7 @@
           <t>C | 488呎 (2房)
 $779万
 $15,964/呎
-(26年-10月-02日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -94569,12 +94529,12 @@
 (26年-10月-12日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$858万
-$19,290/呎
-(在售)</t>
+$730万
+$16,396/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -95122,7 +95082,7 @@
           <t>B | 602呎 (2房)
 $1097万
 $18,223/呎
-(26年-09月-28日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
@@ -95164,12 +95124,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>B | 602呎 (2房)
-招标单位
--
-(在售)</t>
+$1093万
+$18,151/呎
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
@@ -95310,7 +95270,7 @@
           <t>B | 602呎 (2房)
 $1084万
 $18,007/呎
-(26年-10月-05日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
@@ -96071,7 +96031,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96081,7 +96041,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -97129,12 +97089,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
-$883万
-$19,235/呎
-(在售)</t>
+$750万
+$16,350/呎
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -97152,12 +97112,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1543万
+$19,709/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -97278,12 +97238,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1537万
+$19,631/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -97724,7 +97684,7 @@
           <t>B | 783呎 (3房)
 $1516万
 $19,358/呎
-(26年-10月-05日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -97853,12 +97813,12 @@
 (26年-09月-22日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
+$1046万
+$17,648/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -98299,7 +98259,7 @@
           <t>C | 593呎 (2房)
 $1058万
 $17,838/呎
-(26年-09月-28日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -98727,12 +98687,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>B | 783呎 (3房)
-招标单位
--
-(在售)</t>
+$1531万
+$19,557/呎
+(26年-10月-19日)</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
@@ -98858,7 +98818,7 @@
           <t>B | 783呎 (3房)
 $1496万
 $19,102/呎
-(26年-09月-28日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">

--- a/web/files/九龙-将军澳-海瑅湾 II.xlsx
+++ b/web/files/九龙-将军澳-海瑅湾 II.xlsx
@@ -10914,23 +10914,23 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>10262000</v>
+        <v>8722700</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>21742</v>
+        <v>18480</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -29444,34 +29444,34 @@
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
-        <v>8971000</v>
+        <v>7625300</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>19804</v>
+        <v>16833</v>
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K426" s="5" t="n">
-        <v>7625350</v>
+        <v>7625300</v>
       </c>
       <c r="L426" s="5" t="n">
         <v>16833</v>
       </c>
       <c r="M426" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N426" s="3" t="inlineStr">
@@ -30252,34 +30252,34 @@
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
-        <v>8935000</v>
+        <v>7594700</v>
       </c>
       <c r="I438" s="5" t="n">
-        <v>19724</v>
+        <v>16765</v>
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K438" s="5" t="n">
-        <v>7594750</v>
+        <v>7594700</v>
       </c>
       <c r="L438" s="5" t="n">
         <v>16765</v>
       </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N438" s="3" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -32673,7 +32673,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -49591,7 +49591,7 @@
       </c>
       <c r="G723" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H723" s="5" t="n">
@@ -51159,7 +51159,7 @@
       </c>
       <c r="G747" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H747" s="5" t="n">
@@ -56645,14 +56645,14 @@
       </c>
       <c r="G832" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="H832" s="5" t="n">
-        <v>7186200</v>
+        <v>7021000</v>
       </c>
       <c r="I832" s="5" t="n">
-        <v>16149</v>
+        <v>15778</v>
       </c>
       <c r="J832" s="3" t="inlineStr">
         <is>
@@ -56660,10 +56660,10 @@
         </is>
       </c>
       <c r="K832" s="5" t="n">
-        <v>7186200</v>
+        <v>7021000</v>
       </c>
       <c r="L832" s="5" t="n">
-        <v>16149</v>
+        <v>15778</v>
       </c>
       <c r="M832" s="3" t="inlineStr">
         <is>
@@ -67526,34 +67526,34 @@
       </c>
       <c r="F993" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G993" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H993" s="5" t="n">
-        <v>8847000</v>
+        <v>7519900</v>
       </c>
       <c r="I993" s="5" t="n">
-        <v>19275</v>
+        <v>16383</v>
       </c>
       <c r="J993" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K993" s="5" t="n">
-        <v>7519950</v>
+        <v>7519900</v>
       </c>
       <c r="L993" s="5" t="n">
         <v>16383</v>
       </c>
       <c r="M993" s="3" t="inlineStr">
         <is>
-          <t>臨海尊貴120天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N993" s="3" t="inlineStr">
@@ -73537,7 +73537,7 @@
       </c>
       <c r="G1082" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H1082" s="5" t="n">
@@ -87313,7 +87313,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -87323,7 +87323,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -88731,12 +88731,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 472呎 (2房)
-$1026万
-$21,742/呎
-(在售)</t>
+$872万
+$18,480/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -90068,7 +90068,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -90078,7 +90078,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -91480,12 +91480,12 @@
 (26年-10月-08日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$897万
-$19,804/呎
-(在售)</t>
+$763万
+$16,833/呎
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -91590,12 +91590,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$894万
-$19,724/呎
-(在售)</t>
+$759万
+$16,765/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -91870,7 +91870,7 @@
           <t>E | 453呎 (2房)
 $770万
 $16,989/呎
-(26年-10月-12日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -91925,7 +91925,7 @@
           <t>E | 453呎 (2房)
 $750万
 $16,565/呎
-(26年-10月-08日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
@@ -94338,7 +94338,7 @@
           <t>C | 488呎 (2房)
 $782万
 $16,026/呎
-(26年-10月-05日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -94581,7 +94581,7 @@
           <t>D | 445呎 (2房)
 $729万
 $16,371/呎
-(26年-10月-07日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -95378,9 +95378,9 @@
       <c r="E48" s="23" t="inlineStr">
         <is>
           <t>D | 445呎 (2房)
-$719万
-$16,149/呎
-(26年-08月-25日)</t>
+$702万
+$15,778/呎
+(26年-08月-09日)</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
@@ -96031,7 +96031,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -96041,7 +96041,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -97026,12 +97026,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>G | 459呎 (2房)
-$885万
-$19,275/呎
-(在售)</t>
+$752万
+$16,383/呎
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -97747,7 +97747,7 @@
           <t>B | 783呎 (3房)
 $1513万
 $19,319/呎
-(26年-10月-09日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
